--- a/templates/产品明细模板.xlsx
+++ b/templates/产品明细模板.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="29100" windowHeight="13360" activeTab="2"/>
+    <workbookView windowWidth="29100" windowHeight="13300"/>
   </bookViews>
   <sheets>
     <sheet name="明细" sheetId="3" r:id="rId1"/>
@@ -25204,7 +25204,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:AG302"/>
+  <dimension ref="A1:AG141"/>
   <sheetFormatPr defaultColWidth="9.23214285714286" defaultRowHeight="16.8"/>
   <cols>
     <col min="1" max="1" width="54.8571428571429" style="20" customWidth="1"/>
@@ -27318,7 +27318,7 @@
       <c r="S128" s="10"/>
       <c r="T128" s="10"/>
     </row>
-    <row r="129" spans="1:33">
+    <row r="129" spans="1:20">
       <c r="A129" s="24"/>
       <c r="B129" s="24"/>
       <c r="C129" s="24"/>
@@ -27329,7 +27329,7 @@
       <c r="S129" s="10"/>
       <c r="T129" s="10"/>
     </row>
-    <row r="130" spans="1:33">
+    <row r="130" spans="1:20">
       <c r="A130" s="24"/>
       <c r="B130" s="24"/>
       <c r="C130" s="24"/>
@@ -27340,7 +27340,7 @@
       <c r="S130" s="10"/>
       <c r="T130" s="10"/>
     </row>
-    <row r="131" spans="1:33">
+    <row r="131" spans="1:20">
       <c r="A131" s="24"/>
       <c r="B131" s="24"/>
       <c r="C131" s="24"/>
@@ -27351,7 +27351,7 @@
       <c r="S131" s="10"/>
       <c r="T131" s="10"/>
     </row>
-    <row r="132" spans="1:33">
+    <row r="132" spans="1:20">
       <c r="A132" s="24"/>
       <c r="B132" s="24"/>
       <c r="C132" s="24"/>
@@ -27362,7 +27362,7 @@
       <c r="S132" s="10"/>
       <c r="T132" s="10"/>
     </row>
-    <row r="133" s="21" customFormat="1" spans="1:33">
+    <row r="133" s="21" customFormat="1" spans="1:20">
       <c r="A133" s="27"/>
       <c r="B133" s="27"/>
       <c r="C133" s="24"/>
@@ -27382,7 +27382,7 @@
       <c r="S133" s="10"/>
       <c r="T133" s="10"/>
     </row>
-    <row r="134" s="21" customFormat="1" spans="1:33">
+    <row r="134" s="21" customFormat="1" spans="1:20">
       <c r="A134" s="27"/>
       <c r="B134" s="27"/>
       <c r="C134" s="24"/>
@@ -27402,7 +27402,7 @@
       <c r="S134" s="10"/>
       <c r="T134" s="10"/>
     </row>
-    <row r="135" s="21" customFormat="1" spans="1:33">
+    <row r="135" s="21" customFormat="1" spans="1:20">
       <c r="A135" s="27"/>
       <c r="B135" s="27"/>
       <c r="C135" s="24"/>
@@ -27422,7 +27422,7 @@
       <c r="S135" s="10"/>
       <c r="T135" s="10"/>
     </row>
-    <row r="136" s="21" customFormat="1" spans="1:33">
+    <row r="136" s="21" customFormat="1" spans="1:20">
       <c r="A136" s="27"/>
       <c r="B136" s="27"/>
       <c r="C136" s="24"/>
@@ -27442,7 +27442,7 @@
       <c r="S136" s="10"/>
       <c r="T136" s="10"/>
     </row>
-    <row r="137" s="21" customFormat="1" spans="1:33">
+    <row r="137" s="21" customFormat="1" spans="1:20">
       <c r="A137" s="27"/>
       <c r="B137" s="27"/>
       <c r="C137" s="24"/>
@@ -27462,7 +27462,7 @@
       <c r="S137" s="10"/>
       <c r="T137" s="10"/>
     </row>
-    <row r="138" s="21" customFormat="1" spans="1:33">
+    <row r="138" s="21" customFormat="1" spans="1:20">
       <c r="A138" s="27"/>
       <c r="B138" s="27"/>
       <c r="C138" s="24"/>
@@ -27482,7 +27482,7 @@
       <c r="S138" s="10"/>
       <c r="T138" s="10"/>
     </row>
-    <row r="139" s="21" customFormat="1" spans="1:33">
+    <row r="139" s="21" customFormat="1" spans="1:20">
       <c r="A139" s="27"/>
       <c r="B139" s="27"/>
       <c r="C139" s="24"/>
@@ -27502,7 +27502,7 @@
       <c r="S139" s="10"/>
       <c r="T139" s="10"/>
     </row>
-    <row r="140" s="21" customFormat="1" spans="1:33">
+    <row r="140" s="21" customFormat="1" spans="1:20">
       <c r="A140" s="27"/>
       <c r="B140" s="27"/>
       <c r="C140" s="24"/>
@@ -27522,7 +27522,7 @@
       <c r="S140" s="10"/>
       <c r="T140" s="10"/>
     </row>
-    <row r="141" s="21" customFormat="1" spans="1:33">
+    <row r="141" s="21" customFormat="1" spans="1:20">
       <c r="A141" s="27"/>
       <c r="B141" s="27"/>
       <c r="C141" s="24"/>
@@ -27541,2896 +27541,6 @@
       <c r="R141" s="10"/>
       <c r="S141" s="10"/>
       <c r="T141" s="10"/>
-    </row>
-    <row r="142" spans="1:33">
-      <c r="AD142" s="21" t="str" cm="1">
-        <f t="array" ref="AD142">IFERROR(INDEX(商品管理!E:E,MATCH(B142,商品管理!A:A,0)),"")</f>
-        <v/>
-      </c>
-      <c r="AE142" s="21" t="str" cm="1">
-        <f t="array" ref="AE142">IFERROR(INDEX(商品管理!F:F,MATCH(B142,商品管理!A:A,0)),"")</f>
-        <v/>
-      </c>
-      <c r="AF142" s="21" t="str" cm="1">
-        <f t="array" ref="AF142">IFERROR(INDEX(FBA仓库代码表!G:G,MATCH(E142,FBA仓库代码表!B:B,0)),"")</f>
-        <v/>
-      </c>
-      <c r="AG142" s="21" t="str" cm="1">
-        <f t="array" ref="AG142">IFERROR(INDEX(FBA仓库代码表!H:H,MATCH(E142,FBA仓库代码表!B:B,0)),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="143" spans="1:33">
-      <c r="AD143" s="21" t="str" cm="1">
-        <f t="array" ref="AD143">IFERROR(INDEX(商品管理!E:E,MATCH(B143,商品管理!A:A,0)),"")</f>
-        <v/>
-      </c>
-      <c r="AE143" s="21" t="str" cm="1">
-        <f t="array" ref="AE143">IFERROR(INDEX(商品管理!F:F,MATCH(B143,商品管理!A:A,0)),"")</f>
-        <v/>
-      </c>
-      <c r="AF143" s="21" t="str" cm="1">
-        <f t="array" ref="AF143">IFERROR(INDEX(FBA仓库代码表!G:G,MATCH(E143,FBA仓库代码表!B:B,0)),"")</f>
-        <v/>
-      </c>
-      <c r="AG143" s="21" t="str" cm="1">
-        <f t="array" ref="AG143">IFERROR(INDEX(FBA仓库代码表!H:H,MATCH(E143,FBA仓库代码表!B:B,0)),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="144" spans="1:33">
-      <c r="AD144" s="21" t="str" cm="1">
-        <f t="array" ref="AD144">IFERROR(INDEX(商品管理!E:E,MATCH(B144,商品管理!A:A,0)),"")</f>
-        <v/>
-      </c>
-      <c r="AE144" s="21" t="str" cm="1">
-        <f t="array" ref="AE144">IFERROR(INDEX(商品管理!F:F,MATCH(B144,商品管理!A:A,0)),"")</f>
-        <v/>
-      </c>
-      <c r="AF144" s="21" t="str" cm="1">
-        <f t="array" ref="AF144">IFERROR(INDEX(FBA仓库代码表!G:G,MATCH(E144,FBA仓库代码表!B:B,0)),"")</f>
-        <v/>
-      </c>
-      <c r="AG144" s="21" t="str" cm="1">
-        <f t="array" ref="AG144">IFERROR(INDEX(FBA仓库代码表!H:H,MATCH(E144,FBA仓库代码表!B:B,0)),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="145" spans="30:33">
-      <c r="AD145" s="21" t="str" cm="1">
-        <f t="array" ref="AD145">IFERROR(INDEX(商品管理!E:E,MATCH(B145,商品管理!A:A,0)),"")</f>
-        <v/>
-      </c>
-      <c r="AE145" s="21" t="str" cm="1">
-        <f t="array" ref="AE145">IFERROR(INDEX(商品管理!F:F,MATCH(B145,商品管理!A:A,0)),"")</f>
-        <v/>
-      </c>
-      <c r="AF145" s="21" t="str" cm="1">
-        <f t="array" ref="AF145">IFERROR(INDEX(FBA仓库代码表!G:G,MATCH(E145,FBA仓库代码表!B:B,0)),"")</f>
-        <v/>
-      </c>
-      <c r="AG145" s="21" t="str" cm="1">
-        <f t="array" ref="AG145">IFERROR(INDEX(FBA仓库代码表!H:H,MATCH(E145,FBA仓库代码表!B:B,0)),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="146" spans="30:33">
-      <c r="AD146" s="21" t="str" cm="1">
-        <f t="array" ref="AD146">IFERROR(INDEX(商品管理!E:E,MATCH(B146,商品管理!A:A,0)),"")</f>
-        <v/>
-      </c>
-      <c r="AE146" s="21" t="str" cm="1">
-        <f t="array" ref="AE146">IFERROR(INDEX(商品管理!F:F,MATCH(B146,商品管理!A:A,0)),"")</f>
-        <v/>
-      </c>
-      <c r="AF146" s="21" t="str" cm="1">
-        <f t="array" ref="AF146">IFERROR(INDEX(FBA仓库代码表!G:G,MATCH(E146,FBA仓库代码表!B:B,0)),"")</f>
-        <v/>
-      </c>
-      <c r="AG146" s="21" t="str" cm="1">
-        <f t="array" ref="AG146">IFERROR(INDEX(FBA仓库代码表!H:H,MATCH(E146,FBA仓库代码表!B:B,0)),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="147" spans="30:33">
-      <c r="AD147" s="21" t="str" cm="1">
-        <f t="array" ref="AD147">IFERROR(INDEX(商品管理!E:E,MATCH(B147,商品管理!A:A,0)),"")</f>
-        <v/>
-      </c>
-      <c r="AE147" s="21" t="str" cm="1">
-        <f t="array" ref="AE147">IFERROR(INDEX(商品管理!F:F,MATCH(B147,商品管理!A:A,0)),"")</f>
-        <v/>
-      </c>
-      <c r="AF147" s="21" t="str" cm="1">
-        <f t="array" ref="AF147">IFERROR(INDEX(FBA仓库代码表!G:G,MATCH(E147,FBA仓库代码表!B:B,0)),"")</f>
-        <v/>
-      </c>
-      <c r="AG147" s="21" t="str" cm="1">
-        <f t="array" ref="AG147">IFERROR(INDEX(FBA仓库代码表!H:H,MATCH(E147,FBA仓库代码表!B:B,0)),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="148" spans="30:33">
-      <c r="AD148" s="21" t="str" cm="1">
-        <f t="array" ref="AD148">IFERROR(INDEX(商品管理!E:E,MATCH(B148,商品管理!A:A,0)),"")</f>
-        <v/>
-      </c>
-      <c r="AE148" s="21" t="str" cm="1">
-        <f t="array" ref="AE148">IFERROR(INDEX(商品管理!F:F,MATCH(B148,商品管理!A:A,0)),"")</f>
-        <v/>
-      </c>
-      <c r="AF148" s="21" t="str" cm="1">
-        <f t="array" ref="AF148">IFERROR(INDEX(FBA仓库代码表!G:G,MATCH(E148,FBA仓库代码表!B:B,0)),"")</f>
-        <v/>
-      </c>
-      <c r="AG148" s="21" t="str" cm="1">
-        <f t="array" ref="AG148">IFERROR(INDEX(FBA仓库代码表!H:H,MATCH(E148,FBA仓库代码表!B:B,0)),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="149" spans="30:33">
-      <c r="AD149" s="21" t="str" cm="1">
-        <f t="array" ref="AD149">IFERROR(INDEX(商品管理!E:E,MATCH(B149,商品管理!A:A,0)),"")</f>
-        <v/>
-      </c>
-      <c r="AE149" s="21" t="str" cm="1">
-        <f t="array" ref="AE149">IFERROR(INDEX(商品管理!F:F,MATCH(B149,商品管理!A:A,0)),"")</f>
-        <v/>
-      </c>
-      <c r="AF149" s="21" t="str" cm="1">
-        <f t="array" ref="AF149">IFERROR(INDEX(FBA仓库代码表!G:G,MATCH(E149,FBA仓库代码表!B:B,0)),"")</f>
-        <v/>
-      </c>
-      <c r="AG149" s="21" t="str" cm="1">
-        <f t="array" ref="AG149">IFERROR(INDEX(FBA仓库代码表!H:H,MATCH(E149,FBA仓库代码表!B:B,0)),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="150" spans="30:33">
-      <c r="AD150" s="21" t="str" cm="1">
-        <f t="array" ref="AD150">IFERROR(INDEX(商品管理!E:E,MATCH(B150,商品管理!A:A,0)),"")</f>
-        <v/>
-      </c>
-      <c r="AE150" s="21" t="str" cm="1">
-        <f t="array" ref="AE150">IFERROR(INDEX(商品管理!F:F,MATCH(B150,商品管理!A:A,0)),"")</f>
-        <v/>
-      </c>
-      <c r="AF150" s="21" t="str" cm="1">
-        <f t="array" ref="AF150">IFERROR(INDEX(FBA仓库代码表!G:G,MATCH(E150,FBA仓库代码表!B:B,0)),"")</f>
-        <v/>
-      </c>
-      <c r="AG150" s="21" t="str" cm="1">
-        <f t="array" ref="AG150">IFERROR(INDEX(FBA仓库代码表!H:H,MATCH(E150,FBA仓库代码表!B:B,0)),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="151" spans="30:33">
-      <c r="AD151" s="21" t="str" cm="1">
-        <f t="array" ref="AD151">IFERROR(INDEX(商品管理!E:E,MATCH(B151,商品管理!A:A,0)),"")</f>
-        <v/>
-      </c>
-      <c r="AE151" s="21" t="str" cm="1">
-        <f t="array" ref="AE151">IFERROR(INDEX(商品管理!F:F,MATCH(B151,商品管理!A:A,0)),"")</f>
-        <v/>
-      </c>
-      <c r="AF151" s="21" t="str" cm="1">
-        <f t="array" ref="AF151">IFERROR(INDEX(FBA仓库代码表!G:G,MATCH(E151,FBA仓库代码表!B:B,0)),"")</f>
-        <v/>
-      </c>
-      <c r="AG151" s="21" t="str" cm="1">
-        <f t="array" ref="AG151">IFERROR(INDEX(FBA仓库代码表!H:H,MATCH(E151,FBA仓库代码表!B:B,0)),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="152" spans="30:33">
-      <c r="AD152" s="21" t="str" cm="1">
-        <f t="array" ref="AD152">IFERROR(INDEX(商品管理!E:E,MATCH(B152,商品管理!A:A,0)),"")</f>
-        <v/>
-      </c>
-      <c r="AE152" s="21" t="str" cm="1">
-        <f t="array" ref="AE152">IFERROR(INDEX(商品管理!F:F,MATCH(B152,商品管理!A:A,0)),"")</f>
-        <v/>
-      </c>
-      <c r="AF152" s="21" t="str" cm="1">
-        <f t="array" ref="AF152">IFERROR(INDEX(FBA仓库代码表!G:G,MATCH(E152,FBA仓库代码表!B:B,0)),"")</f>
-        <v/>
-      </c>
-      <c r="AG152" s="21" t="str" cm="1">
-        <f t="array" ref="AG152">IFERROR(INDEX(FBA仓库代码表!H:H,MATCH(E152,FBA仓库代码表!B:B,0)),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="153" spans="30:33">
-      <c r="AD153" s="21" t="str" cm="1">
-        <f t="array" ref="AD153">IFERROR(INDEX(商品管理!E:E,MATCH(B153,商品管理!A:A,0)),"")</f>
-        <v/>
-      </c>
-      <c r="AE153" s="21" t="str" cm="1">
-        <f t="array" ref="AE153">IFERROR(INDEX(商品管理!F:F,MATCH(B153,商品管理!A:A,0)),"")</f>
-        <v/>
-      </c>
-      <c r="AF153" s="21" t="str" cm="1">
-        <f t="array" ref="AF153">IFERROR(INDEX(FBA仓库代码表!G:G,MATCH(E153,FBA仓库代码表!B:B,0)),"")</f>
-        <v/>
-      </c>
-      <c r="AG153" s="21" t="str" cm="1">
-        <f t="array" ref="AG153">IFERROR(INDEX(FBA仓库代码表!H:H,MATCH(E153,FBA仓库代码表!B:B,0)),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="154" spans="30:33">
-      <c r="AD154" s="21" t="str" cm="1">
-        <f t="array" ref="AD154">IFERROR(INDEX(商品管理!E:E,MATCH(B154,商品管理!A:A,0)),"")</f>
-        <v/>
-      </c>
-      <c r="AE154" s="21" t="str" cm="1">
-        <f t="array" ref="AE154">IFERROR(INDEX(商品管理!F:F,MATCH(B154,商品管理!A:A,0)),"")</f>
-        <v/>
-      </c>
-      <c r="AF154" s="21" t="str" cm="1">
-        <f t="array" ref="AF154">IFERROR(INDEX(FBA仓库代码表!G:G,MATCH(E154,FBA仓库代码表!B:B,0)),"")</f>
-        <v/>
-      </c>
-      <c r="AG154" s="21" t="str" cm="1">
-        <f t="array" ref="AG154">IFERROR(INDEX(FBA仓库代码表!H:H,MATCH(E154,FBA仓库代码表!B:B,0)),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="155" spans="30:33">
-      <c r="AD155" s="21" t="str" cm="1">
-        <f t="array" ref="AD155">IFERROR(INDEX(商品管理!E:E,MATCH(B155,商品管理!A:A,0)),"")</f>
-        <v/>
-      </c>
-      <c r="AE155" s="21" t="str" cm="1">
-        <f t="array" ref="AE155">IFERROR(INDEX(商品管理!F:F,MATCH(B155,商品管理!A:A,0)),"")</f>
-        <v/>
-      </c>
-      <c r="AF155" s="21" t="str" cm="1">
-        <f t="array" ref="AF155">IFERROR(INDEX(FBA仓库代码表!G:G,MATCH(E155,FBA仓库代码表!B:B,0)),"")</f>
-        <v/>
-      </c>
-      <c r="AG155" s="21" t="str" cm="1">
-        <f t="array" ref="AG155">IFERROR(INDEX(FBA仓库代码表!H:H,MATCH(E155,FBA仓库代码表!B:B,0)),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="156" spans="30:33">
-      <c r="AD156" s="21" t="str" cm="1">
-        <f t="array" ref="AD156">IFERROR(INDEX(商品管理!E:E,MATCH(B156,商品管理!A:A,0)),"")</f>
-        <v/>
-      </c>
-      <c r="AE156" s="21" t="str" cm="1">
-        <f t="array" ref="AE156">IFERROR(INDEX(商品管理!F:F,MATCH(B156,商品管理!A:A,0)),"")</f>
-        <v/>
-      </c>
-      <c r="AF156" s="21" t="str" cm="1">
-        <f t="array" ref="AF156">IFERROR(INDEX(FBA仓库代码表!G:G,MATCH(E156,FBA仓库代码表!B:B,0)),"")</f>
-        <v/>
-      </c>
-      <c r="AG156" s="21" t="str" cm="1">
-        <f t="array" ref="AG156">IFERROR(INDEX(FBA仓库代码表!H:H,MATCH(E156,FBA仓库代码表!B:B,0)),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="157" spans="30:33">
-      <c r="AD157" s="21" t="str" cm="1">
-        <f t="array" ref="AD157">IFERROR(INDEX(商品管理!E:E,MATCH(B157,商品管理!A:A,0)),"")</f>
-        <v/>
-      </c>
-      <c r="AE157" s="21" t="str" cm="1">
-        <f t="array" ref="AE157">IFERROR(INDEX(商品管理!F:F,MATCH(B157,商品管理!A:A,0)),"")</f>
-        <v/>
-      </c>
-      <c r="AF157" s="21" t="str" cm="1">
-        <f t="array" ref="AF157">IFERROR(INDEX(FBA仓库代码表!G:G,MATCH(E157,FBA仓库代码表!B:B,0)),"")</f>
-        <v/>
-      </c>
-      <c r="AG157" s="21" t="str" cm="1">
-        <f t="array" ref="AG157">IFERROR(INDEX(FBA仓库代码表!H:H,MATCH(E157,FBA仓库代码表!B:B,0)),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="158" spans="30:33">
-      <c r="AD158" s="21" t="str" cm="1">
-        <f t="array" ref="AD158">IFERROR(INDEX(商品管理!E:E,MATCH(B158,商品管理!A:A,0)),"")</f>
-        <v/>
-      </c>
-      <c r="AE158" s="21" t="str" cm="1">
-        <f t="array" ref="AE158">IFERROR(INDEX(商品管理!F:F,MATCH(B158,商品管理!A:A,0)),"")</f>
-        <v/>
-      </c>
-      <c r="AF158" s="21" t="str" cm="1">
-        <f t="array" ref="AF158">IFERROR(INDEX(FBA仓库代码表!G:G,MATCH(E158,FBA仓库代码表!B:B,0)),"")</f>
-        <v/>
-      </c>
-      <c r="AG158" s="21" t="str" cm="1">
-        <f t="array" ref="AG158">IFERROR(INDEX(FBA仓库代码表!H:H,MATCH(E158,FBA仓库代码表!B:B,0)),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="159" spans="30:33">
-      <c r="AD159" s="21" t="str" cm="1">
-        <f t="array" ref="AD159">IFERROR(INDEX(商品管理!E:E,MATCH(B159,商品管理!A:A,0)),"")</f>
-        <v/>
-      </c>
-      <c r="AE159" s="21" t="str" cm="1">
-        <f t="array" ref="AE159">IFERROR(INDEX(商品管理!F:F,MATCH(B159,商品管理!A:A,0)),"")</f>
-        <v/>
-      </c>
-      <c r="AF159" s="21" t="str" cm="1">
-        <f t="array" ref="AF159">IFERROR(INDEX(FBA仓库代码表!G:G,MATCH(E159,FBA仓库代码表!B:B,0)),"")</f>
-        <v/>
-      </c>
-      <c r="AG159" s="21" t="str" cm="1">
-        <f t="array" ref="AG159">IFERROR(INDEX(FBA仓库代码表!H:H,MATCH(E159,FBA仓库代码表!B:B,0)),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="160" spans="30:33">
-      <c r="AD160" s="21" t="str" cm="1">
-        <f t="array" ref="AD160">IFERROR(INDEX(商品管理!E:E,MATCH(B160,商品管理!A:A,0)),"")</f>
-        <v/>
-      </c>
-      <c r="AE160" s="21" t="str" cm="1">
-        <f t="array" ref="AE160">IFERROR(INDEX(商品管理!F:F,MATCH(B160,商品管理!A:A,0)),"")</f>
-        <v/>
-      </c>
-      <c r="AF160" s="21" t="str" cm="1">
-        <f t="array" ref="AF160">IFERROR(INDEX(FBA仓库代码表!G:G,MATCH(E160,FBA仓库代码表!B:B,0)),"")</f>
-        <v/>
-      </c>
-      <c r="AG160" s="21" t="str" cm="1">
-        <f t="array" ref="AG160">IFERROR(INDEX(FBA仓库代码表!H:H,MATCH(E160,FBA仓库代码表!B:B,0)),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="161" spans="30:33">
-      <c r="AD161" s="21" t="str" cm="1">
-        <f t="array" ref="AD161">IFERROR(INDEX(商品管理!E:E,MATCH(B161,商品管理!A:A,0)),"")</f>
-        <v/>
-      </c>
-      <c r="AE161" s="21" t="str" cm="1">
-        <f t="array" ref="AE161">IFERROR(INDEX(商品管理!F:F,MATCH(B161,商品管理!A:A,0)),"")</f>
-        <v/>
-      </c>
-      <c r="AF161" s="21" t="str" cm="1">
-        <f t="array" ref="AF161">IFERROR(INDEX(FBA仓库代码表!G:G,MATCH(E161,FBA仓库代码表!B:B,0)),"")</f>
-        <v/>
-      </c>
-      <c r="AG161" s="21" t="str" cm="1">
-        <f t="array" ref="AG161">IFERROR(INDEX(FBA仓库代码表!H:H,MATCH(E161,FBA仓库代码表!B:B,0)),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="162" spans="30:33">
-      <c r="AD162" s="21" t="str" cm="1">
-        <f t="array" ref="AD162">IFERROR(INDEX(商品管理!E:E,MATCH(B162,商品管理!A:A,0)),"")</f>
-        <v/>
-      </c>
-      <c r="AE162" s="21" t="str" cm="1">
-        <f t="array" ref="AE162">IFERROR(INDEX(商品管理!F:F,MATCH(B162,商品管理!A:A,0)),"")</f>
-        <v/>
-      </c>
-      <c r="AF162" s="21" t="str" cm="1">
-        <f t="array" ref="AF162">IFERROR(INDEX(FBA仓库代码表!G:G,MATCH(E162,FBA仓库代码表!B:B,0)),"")</f>
-        <v/>
-      </c>
-      <c r="AG162" s="21" t="str" cm="1">
-        <f t="array" ref="AG162">IFERROR(INDEX(FBA仓库代码表!H:H,MATCH(E162,FBA仓库代码表!B:B,0)),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="163" spans="30:33">
-      <c r="AD163" s="21" t="str" cm="1">
-        <f t="array" ref="AD163">IFERROR(INDEX(商品管理!E:E,MATCH(B163,商品管理!A:A,0)),"")</f>
-        <v/>
-      </c>
-      <c r="AE163" s="21" t="str" cm="1">
-        <f t="array" ref="AE163">IFERROR(INDEX(商品管理!F:F,MATCH(B163,商品管理!A:A,0)),"")</f>
-        <v/>
-      </c>
-      <c r="AF163" s="21" t="str" cm="1">
-        <f t="array" ref="AF163">IFERROR(INDEX(FBA仓库代码表!G:G,MATCH(E163,FBA仓库代码表!B:B,0)),"")</f>
-        <v/>
-      </c>
-      <c r="AG163" s="21" t="str" cm="1">
-        <f t="array" ref="AG163">IFERROR(INDEX(FBA仓库代码表!H:H,MATCH(E163,FBA仓库代码表!B:B,0)),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="164" spans="30:33">
-      <c r="AD164" s="21" t="str" cm="1">
-        <f t="array" ref="AD164">IFERROR(INDEX(商品管理!E:E,MATCH(B164,商品管理!A:A,0)),"")</f>
-        <v/>
-      </c>
-      <c r="AE164" s="21" t="str" cm="1">
-        <f t="array" ref="AE164">IFERROR(INDEX(商品管理!F:F,MATCH(B164,商品管理!A:A,0)),"")</f>
-        <v/>
-      </c>
-      <c r="AF164" s="21" t="str" cm="1">
-        <f t="array" ref="AF164">IFERROR(INDEX(FBA仓库代码表!G:G,MATCH(E164,FBA仓库代码表!B:B,0)),"")</f>
-        <v/>
-      </c>
-      <c r="AG164" s="21" t="str" cm="1">
-        <f t="array" ref="AG164">IFERROR(INDEX(FBA仓库代码表!H:H,MATCH(E164,FBA仓库代码表!B:B,0)),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="165" spans="30:33">
-      <c r="AD165" s="21" t="str" cm="1">
-        <f t="array" ref="AD165">IFERROR(INDEX(商品管理!E:E,MATCH(B165,商品管理!A:A,0)),"")</f>
-        <v/>
-      </c>
-      <c r="AE165" s="21" t="str" cm="1">
-        <f t="array" ref="AE165">IFERROR(INDEX(商品管理!F:F,MATCH(B165,商品管理!A:A,0)),"")</f>
-        <v/>
-      </c>
-      <c r="AF165" s="21" t="str" cm="1">
-        <f t="array" ref="AF165">IFERROR(INDEX(FBA仓库代码表!G:G,MATCH(E165,FBA仓库代码表!B:B,0)),"")</f>
-        <v/>
-      </c>
-      <c r="AG165" s="21" t="str" cm="1">
-        <f t="array" ref="AG165">IFERROR(INDEX(FBA仓库代码表!H:H,MATCH(E165,FBA仓库代码表!B:B,0)),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="166" spans="30:33">
-      <c r="AD166" s="21" t="str" cm="1">
-        <f t="array" ref="AD166">IFERROR(INDEX(商品管理!E:E,MATCH(B166,商品管理!A:A,0)),"")</f>
-        <v/>
-      </c>
-      <c r="AE166" s="21" t="str" cm="1">
-        <f t="array" ref="AE166">IFERROR(INDEX(商品管理!F:F,MATCH(B166,商品管理!A:A,0)),"")</f>
-        <v/>
-      </c>
-      <c r="AF166" s="21" t="str" cm="1">
-        <f t="array" ref="AF166">IFERROR(INDEX(FBA仓库代码表!G:G,MATCH(E166,FBA仓库代码表!B:B,0)),"")</f>
-        <v/>
-      </c>
-      <c r="AG166" s="21" t="str" cm="1">
-        <f t="array" ref="AG166">IFERROR(INDEX(FBA仓库代码表!H:H,MATCH(E166,FBA仓库代码表!B:B,0)),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="167" spans="30:33">
-      <c r="AD167" s="21" t="str" cm="1">
-        <f t="array" ref="AD167">IFERROR(INDEX(商品管理!E:E,MATCH(B167,商品管理!A:A,0)),"")</f>
-        <v/>
-      </c>
-      <c r="AE167" s="21" t="str" cm="1">
-        <f t="array" ref="AE167">IFERROR(INDEX(商品管理!F:F,MATCH(B167,商品管理!A:A,0)),"")</f>
-        <v/>
-      </c>
-      <c r="AF167" s="21" t="str" cm="1">
-        <f t="array" ref="AF167">IFERROR(INDEX(FBA仓库代码表!G:G,MATCH(E167,FBA仓库代码表!B:B,0)),"")</f>
-        <v/>
-      </c>
-      <c r="AG167" s="21" t="str" cm="1">
-        <f t="array" ref="AG167">IFERROR(INDEX(FBA仓库代码表!H:H,MATCH(E167,FBA仓库代码表!B:B,0)),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="168" spans="30:33">
-      <c r="AD168" s="21" t="str" cm="1">
-        <f t="array" ref="AD168">IFERROR(INDEX(商品管理!E:E,MATCH(B168,商品管理!A:A,0)),"")</f>
-        <v/>
-      </c>
-      <c r="AE168" s="21" t="str" cm="1">
-        <f t="array" ref="AE168">IFERROR(INDEX(商品管理!F:F,MATCH(B168,商品管理!A:A,0)),"")</f>
-        <v/>
-      </c>
-      <c r="AF168" s="21" t="str" cm="1">
-        <f t="array" ref="AF168">IFERROR(INDEX(FBA仓库代码表!G:G,MATCH(E168,FBA仓库代码表!B:B,0)),"")</f>
-        <v/>
-      </c>
-      <c r="AG168" s="21" t="str" cm="1">
-        <f t="array" ref="AG168">IFERROR(INDEX(FBA仓库代码表!H:H,MATCH(E168,FBA仓库代码表!B:B,0)),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="169" spans="30:33">
-      <c r="AD169" s="21" t="str" cm="1">
-        <f t="array" ref="AD169">IFERROR(INDEX(商品管理!E:E,MATCH(B169,商品管理!A:A,0)),"")</f>
-        <v/>
-      </c>
-      <c r="AE169" s="21" t="str" cm="1">
-        <f t="array" ref="AE169">IFERROR(INDEX(商品管理!F:F,MATCH(B169,商品管理!A:A,0)),"")</f>
-        <v/>
-      </c>
-      <c r="AF169" s="21" t="str" cm="1">
-        <f t="array" ref="AF169">IFERROR(INDEX(FBA仓库代码表!G:G,MATCH(E169,FBA仓库代码表!B:B,0)),"")</f>
-        <v/>
-      </c>
-      <c r="AG169" s="21" t="str" cm="1">
-        <f t="array" ref="AG169">IFERROR(INDEX(FBA仓库代码表!H:H,MATCH(E169,FBA仓库代码表!B:B,0)),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="170" spans="30:33">
-      <c r="AD170" s="21" t="str" cm="1">
-        <f t="array" ref="AD170">IFERROR(INDEX(商品管理!E:E,MATCH(B170,商品管理!A:A,0)),"")</f>
-        <v/>
-      </c>
-      <c r="AE170" s="21" t="str" cm="1">
-        <f t="array" ref="AE170">IFERROR(INDEX(商品管理!F:F,MATCH(B170,商品管理!A:A,0)),"")</f>
-        <v/>
-      </c>
-      <c r="AF170" s="21" t="str" cm="1">
-        <f t="array" ref="AF170">IFERROR(INDEX(FBA仓库代码表!G:G,MATCH(E170,FBA仓库代码表!B:B,0)),"")</f>
-        <v/>
-      </c>
-      <c r="AG170" s="21" t="str" cm="1">
-        <f t="array" ref="AG170">IFERROR(INDEX(FBA仓库代码表!H:H,MATCH(E170,FBA仓库代码表!B:B,0)),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="171" spans="30:33">
-      <c r="AD171" s="21" t="str" cm="1">
-        <f t="array" ref="AD171">IFERROR(INDEX(商品管理!E:E,MATCH(B171,商品管理!A:A,0)),"")</f>
-        <v/>
-      </c>
-      <c r="AE171" s="21" t="str" cm="1">
-        <f t="array" ref="AE171">IFERROR(INDEX(商品管理!F:F,MATCH(B171,商品管理!A:A,0)),"")</f>
-        <v/>
-      </c>
-      <c r="AF171" s="21" t="str" cm="1">
-        <f t="array" ref="AF171">IFERROR(INDEX(FBA仓库代码表!G:G,MATCH(E171,FBA仓库代码表!B:B,0)),"")</f>
-        <v/>
-      </c>
-      <c r="AG171" s="21" t="str" cm="1">
-        <f t="array" ref="AG171">IFERROR(INDEX(FBA仓库代码表!H:H,MATCH(E171,FBA仓库代码表!B:B,0)),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="172" spans="30:33">
-      <c r="AD172" s="21" t="str" cm="1">
-        <f t="array" ref="AD172">IFERROR(INDEX(商品管理!E:E,MATCH(B172,商品管理!A:A,0)),"")</f>
-        <v/>
-      </c>
-      <c r="AE172" s="21" t="str" cm="1">
-        <f t="array" ref="AE172">IFERROR(INDEX(商品管理!F:F,MATCH(B172,商品管理!A:A,0)),"")</f>
-        <v/>
-      </c>
-      <c r="AF172" s="21" t="str" cm="1">
-        <f t="array" ref="AF172">IFERROR(INDEX(FBA仓库代码表!G:G,MATCH(E172,FBA仓库代码表!B:B,0)),"")</f>
-        <v/>
-      </c>
-      <c r="AG172" s="21" t="str" cm="1">
-        <f t="array" ref="AG172">IFERROR(INDEX(FBA仓库代码表!H:H,MATCH(E172,FBA仓库代码表!B:B,0)),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="173" spans="30:33">
-      <c r="AD173" s="21" t="str" cm="1">
-        <f t="array" ref="AD173">IFERROR(INDEX(商品管理!E:E,MATCH(B173,商品管理!A:A,0)),"")</f>
-        <v/>
-      </c>
-      <c r="AE173" s="21" t="str" cm="1">
-        <f t="array" ref="AE173">IFERROR(INDEX(商品管理!F:F,MATCH(B173,商品管理!A:A,0)),"")</f>
-        <v/>
-      </c>
-      <c r="AF173" s="21" t="str" cm="1">
-        <f t="array" ref="AF173">IFERROR(INDEX(FBA仓库代码表!G:G,MATCH(E173,FBA仓库代码表!B:B,0)),"")</f>
-        <v/>
-      </c>
-      <c r="AG173" s="21" t="str" cm="1">
-        <f t="array" ref="AG173">IFERROR(INDEX(FBA仓库代码表!H:H,MATCH(E173,FBA仓库代码表!B:B,0)),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="174" spans="30:33">
-      <c r="AD174" s="21" t="str" cm="1">
-        <f t="array" ref="AD174">IFERROR(INDEX(商品管理!E:E,MATCH(B174,商品管理!A:A,0)),"")</f>
-        <v/>
-      </c>
-      <c r="AE174" s="21" t="str" cm="1">
-        <f t="array" ref="AE174">IFERROR(INDEX(商品管理!F:F,MATCH(B174,商品管理!A:A,0)),"")</f>
-        <v/>
-      </c>
-      <c r="AF174" s="21" t="str" cm="1">
-        <f t="array" ref="AF174">IFERROR(INDEX(FBA仓库代码表!G:G,MATCH(E174,FBA仓库代码表!B:B,0)),"")</f>
-        <v/>
-      </c>
-      <c r="AG174" s="21" t="str" cm="1">
-        <f t="array" ref="AG174">IFERROR(INDEX(FBA仓库代码表!H:H,MATCH(E174,FBA仓库代码表!B:B,0)),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="175" spans="30:33">
-      <c r="AD175" s="21" t="str" cm="1">
-        <f t="array" ref="AD175">IFERROR(INDEX(商品管理!E:E,MATCH(B175,商品管理!A:A,0)),"")</f>
-        <v/>
-      </c>
-      <c r="AE175" s="21" t="str" cm="1">
-        <f t="array" ref="AE175">IFERROR(INDEX(商品管理!F:F,MATCH(B175,商品管理!A:A,0)),"")</f>
-        <v/>
-      </c>
-      <c r="AF175" s="21" t="str" cm="1">
-        <f t="array" ref="AF175">IFERROR(INDEX(FBA仓库代码表!G:G,MATCH(E175,FBA仓库代码表!B:B,0)),"")</f>
-        <v/>
-      </c>
-      <c r="AG175" s="21" t="str" cm="1">
-        <f t="array" ref="AG175">IFERROR(INDEX(FBA仓库代码表!H:H,MATCH(E175,FBA仓库代码表!B:B,0)),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="176" spans="30:33">
-      <c r="AD176" s="21" t="str" cm="1">
-        <f t="array" ref="AD176">IFERROR(INDEX(商品管理!E:E,MATCH(B176,商品管理!A:A,0)),"")</f>
-        <v/>
-      </c>
-      <c r="AE176" s="21" t="str" cm="1">
-        <f t="array" ref="AE176">IFERROR(INDEX(商品管理!F:F,MATCH(B176,商品管理!A:A,0)),"")</f>
-        <v/>
-      </c>
-      <c r="AF176" s="21" t="str" cm="1">
-        <f t="array" ref="AF176">IFERROR(INDEX(FBA仓库代码表!G:G,MATCH(E176,FBA仓库代码表!B:B,0)),"")</f>
-        <v/>
-      </c>
-      <c r="AG176" s="21" t="str" cm="1">
-        <f t="array" ref="AG176">IFERROR(INDEX(FBA仓库代码表!H:H,MATCH(E176,FBA仓库代码表!B:B,0)),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="177" spans="30:33">
-      <c r="AD177" s="21" t="str" cm="1">
-        <f t="array" ref="AD177">IFERROR(INDEX(商品管理!E:E,MATCH(B177,商品管理!A:A,0)),"")</f>
-        <v/>
-      </c>
-      <c r="AE177" s="21" t="str" cm="1">
-        <f t="array" ref="AE177">IFERROR(INDEX(商品管理!F:F,MATCH(B177,商品管理!A:A,0)),"")</f>
-        <v/>
-      </c>
-      <c r="AF177" s="21" t="str" cm="1">
-        <f t="array" ref="AF177">IFERROR(INDEX(FBA仓库代码表!G:G,MATCH(E177,FBA仓库代码表!B:B,0)),"")</f>
-        <v/>
-      </c>
-      <c r="AG177" s="21" t="str" cm="1">
-        <f t="array" ref="AG177">IFERROR(INDEX(FBA仓库代码表!H:H,MATCH(E177,FBA仓库代码表!B:B,0)),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="178" spans="30:33">
-      <c r="AD178" s="21" t="str" cm="1">
-        <f t="array" ref="AD178">IFERROR(INDEX(商品管理!E:E,MATCH(B178,商品管理!A:A,0)),"")</f>
-        <v/>
-      </c>
-      <c r="AE178" s="21" t="str" cm="1">
-        <f t="array" ref="AE178">IFERROR(INDEX(商品管理!F:F,MATCH(B178,商品管理!A:A,0)),"")</f>
-        <v/>
-      </c>
-      <c r="AF178" s="21" t="str" cm="1">
-        <f t="array" ref="AF178">IFERROR(INDEX(FBA仓库代码表!G:G,MATCH(E178,FBA仓库代码表!B:B,0)),"")</f>
-        <v/>
-      </c>
-      <c r="AG178" s="21" t="str" cm="1">
-        <f t="array" ref="AG178">IFERROR(INDEX(FBA仓库代码表!H:H,MATCH(E178,FBA仓库代码表!B:B,0)),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="179" spans="30:33">
-      <c r="AD179" s="21" t="str" cm="1">
-        <f t="array" ref="AD179">IFERROR(INDEX(商品管理!E:E,MATCH(B179,商品管理!A:A,0)),"")</f>
-        <v/>
-      </c>
-      <c r="AE179" s="21" t="str" cm="1">
-        <f t="array" ref="AE179">IFERROR(INDEX(商品管理!F:F,MATCH(B179,商品管理!A:A,0)),"")</f>
-        <v/>
-      </c>
-      <c r="AF179" s="21" t="str" cm="1">
-        <f t="array" ref="AF179">IFERROR(INDEX(FBA仓库代码表!G:G,MATCH(E179,FBA仓库代码表!B:B,0)),"")</f>
-        <v/>
-      </c>
-      <c r="AG179" s="21" t="str" cm="1">
-        <f t="array" ref="AG179">IFERROR(INDEX(FBA仓库代码表!H:H,MATCH(E179,FBA仓库代码表!B:B,0)),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="180" spans="30:33">
-      <c r="AD180" s="21" t="str" cm="1">
-        <f t="array" ref="AD180">IFERROR(INDEX(商品管理!E:E,MATCH(B180,商品管理!A:A,0)),"")</f>
-        <v/>
-      </c>
-      <c r="AE180" s="21" t="str" cm="1">
-        <f t="array" ref="AE180">IFERROR(INDEX(商品管理!F:F,MATCH(B180,商品管理!A:A,0)),"")</f>
-        <v/>
-      </c>
-      <c r="AF180" s="21" t="str" cm="1">
-        <f t="array" ref="AF180">IFERROR(INDEX(FBA仓库代码表!G:G,MATCH(E180,FBA仓库代码表!B:B,0)),"")</f>
-        <v/>
-      </c>
-      <c r="AG180" s="21" t="str" cm="1">
-        <f t="array" ref="AG180">IFERROR(INDEX(FBA仓库代码表!H:H,MATCH(E180,FBA仓库代码表!B:B,0)),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="181" spans="30:33">
-      <c r="AD181" s="21" t="str" cm="1">
-        <f t="array" ref="AD181">IFERROR(INDEX(商品管理!E:E,MATCH(B181,商品管理!A:A,0)),"")</f>
-        <v/>
-      </c>
-      <c r="AE181" s="21" t="str" cm="1">
-        <f t="array" ref="AE181">IFERROR(INDEX(商品管理!F:F,MATCH(B181,商品管理!A:A,0)),"")</f>
-        <v/>
-      </c>
-      <c r="AF181" s="21" t="str" cm="1">
-        <f t="array" ref="AF181">IFERROR(INDEX(FBA仓库代码表!G:G,MATCH(E181,FBA仓库代码表!B:B,0)),"")</f>
-        <v/>
-      </c>
-      <c r="AG181" s="21" t="str" cm="1">
-        <f t="array" ref="AG181">IFERROR(INDEX(FBA仓库代码表!H:H,MATCH(E181,FBA仓库代码表!B:B,0)),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="182" spans="30:33">
-      <c r="AD182" s="21" t="str" cm="1">
-        <f t="array" ref="AD182">IFERROR(INDEX(商品管理!E:E,MATCH(B182,商品管理!A:A,0)),"")</f>
-        <v/>
-      </c>
-      <c r="AE182" s="21" t="str" cm="1">
-        <f t="array" ref="AE182">IFERROR(INDEX(商品管理!F:F,MATCH(B182,商品管理!A:A,0)),"")</f>
-        <v/>
-      </c>
-      <c r="AF182" s="21" t="str" cm="1">
-        <f t="array" ref="AF182">IFERROR(INDEX(FBA仓库代码表!G:G,MATCH(E182,FBA仓库代码表!B:B,0)),"")</f>
-        <v/>
-      </c>
-      <c r="AG182" s="21" t="str" cm="1">
-        <f t="array" ref="AG182">IFERROR(INDEX(FBA仓库代码表!H:H,MATCH(E182,FBA仓库代码表!B:B,0)),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="183" spans="30:33">
-      <c r="AD183" s="21" t="str" cm="1">
-        <f t="array" ref="AD183">IFERROR(INDEX(商品管理!E:E,MATCH(B183,商品管理!A:A,0)),"")</f>
-        <v/>
-      </c>
-      <c r="AE183" s="21" t="str" cm="1">
-        <f t="array" ref="AE183">IFERROR(INDEX(商品管理!F:F,MATCH(B183,商品管理!A:A,0)),"")</f>
-        <v/>
-      </c>
-      <c r="AF183" s="21" t="str" cm="1">
-        <f t="array" ref="AF183">IFERROR(INDEX(FBA仓库代码表!G:G,MATCH(E183,FBA仓库代码表!B:B,0)),"")</f>
-        <v/>
-      </c>
-      <c r="AG183" s="21" t="str" cm="1">
-        <f t="array" ref="AG183">IFERROR(INDEX(FBA仓库代码表!H:H,MATCH(E183,FBA仓库代码表!B:B,0)),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="184" spans="30:33">
-      <c r="AD184" s="21" t="str" cm="1">
-        <f t="array" ref="AD184">IFERROR(INDEX(商品管理!E:E,MATCH(B184,商品管理!A:A,0)),"")</f>
-        <v/>
-      </c>
-      <c r="AE184" s="21" t="str" cm="1">
-        <f t="array" ref="AE184">IFERROR(INDEX(商品管理!F:F,MATCH(B184,商品管理!A:A,0)),"")</f>
-        <v/>
-      </c>
-      <c r="AF184" s="21" t="str" cm="1">
-        <f t="array" ref="AF184">IFERROR(INDEX(FBA仓库代码表!G:G,MATCH(E184,FBA仓库代码表!B:B,0)),"")</f>
-        <v/>
-      </c>
-      <c r="AG184" s="21" t="str" cm="1">
-        <f t="array" ref="AG184">IFERROR(INDEX(FBA仓库代码表!H:H,MATCH(E184,FBA仓库代码表!B:B,0)),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="185" spans="30:33">
-      <c r="AD185" s="21" t="str" cm="1">
-        <f t="array" ref="AD185">IFERROR(INDEX(商品管理!E:E,MATCH(B185,商品管理!A:A,0)),"")</f>
-        <v/>
-      </c>
-      <c r="AE185" s="21" t="str" cm="1">
-        <f t="array" ref="AE185">IFERROR(INDEX(商品管理!F:F,MATCH(B185,商品管理!A:A,0)),"")</f>
-        <v/>
-      </c>
-      <c r="AF185" s="21" t="str" cm="1">
-        <f t="array" ref="AF185">IFERROR(INDEX(FBA仓库代码表!G:G,MATCH(E185,FBA仓库代码表!B:B,0)),"")</f>
-        <v/>
-      </c>
-      <c r="AG185" s="21" t="str" cm="1">
-        <f t="array" ref="AG185">IFERROR(INDEX(FBA仓库代码表!H:H,MATCH(E185,FBA仓库代码表!B:B,0)),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="186" spans="30:33">
-      <c r="AD186" s="21" t="str" cm="1">
-        <f t="array" ref="AD186">IFERROR(INDEX(商品管理!E:E,MATCH(B186,商品管理!A:A,0)),"")</f>
-        <v/>
-      </c>
-      <c r="AE186" s="21" t="str" cm="1">
-        <f t="array" ref="AE186">IFERROR(INDEX(商品管理!F:F,MATCH(B186,商品管理!A:A,0)),"")</f>
-        <v/>
-      </c>
-      <c r="AF186" s="21" t="str" cm="1">
-        <f t="array" ref="AF186">IFERROR(INDEX(FBA仓库代码表!G:G,MATCH(E186,FBA仓库代码表!B:B,0)),"")</f>
-        <v/>
-      </c>
-      <c r="AG186" s="21" t="str" cm="1">
-        <f t="array" ref="AG186">IFERROR(INDEX(FBA仓库代码表!H:H,MATCH(E186,FBA仓库代码表!B:B,0)),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="187" spans="30:33">
-      <c r="AD187" s="21" t="str" cm="1">
-        <f t="array" ref="AD187">IFERROR(INDEX(商品管理!E:E,MATCH(B187,商品管理!A:A,0)),"")</f>
-        <v/>
-      </c>
-      <c r="AE187" s="21" t="str" cm="1">
-        <f t="array" ref="AE187">IFERROR(INDEX(商品管理!F:F,MATCH(B187,商品管理!A:A,0)),"")</f>
-        <v/>
-      </c>
-      <c r="AF187" s="21" t="str" cm="1">
-        <f t="array" ref="AF187">IFERROR(INDEX(FBA仓库代码表!G:G,MATCH(E187,FBA仓库代码表!B:B,0)),"")</f>
-        <v/>
-      </c>
-      <c r="AG187" s="21" t="str" cm="1">
-        <f t="array" ref="AG187">IFERROR(INDEX(FBA仓库代码表!H:H,MATCH(E187,FBA仓库代码表!B:B,0)),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="188" spans="30:33">
-      <c r="AD188" s="21" t="str" cm="1">
-        <f t="array" ref="AD188">IFERROR(INDEX(商品管理!E:E,MATCH(B188,商品管理!A:A,0)),"")</f>
-        <v/>
-      </c>
-      <c r="AE188" s="21" t="str" cm="1">
-        <f t="array" ref="AE188">IFERROR(INDEX(商品管理!F:F,MATCH(B188,商品管理!A:A,0)),"")</f>
-        <v/>
-      </c>
-      <c r="AF188" s="21" t="str" cm="1">
-        <f t="array" ref="AF188">IFERROR(INDEX(FBA仓库代码表!G:G,MATCH(E188,FBA仓库代码表!B:B,0)),"")</f>
-        <v/>
-      </c>
-      <c r="AG188" s="21" t="str" cm="1">
-        <f t="array" ref="AG188">IFERROR(INDEX(FBA仓库代码表!H:H,MATCH(E188,FBA仓库代码表!B:B,0)),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="189" spans="30:33">
-      <c r="AD189" s="21" t="str" cm="1">
-        <f t="array" ref="AD189">IFERROR(INDEX(商品管理!E:E,MATCH(B189,商品管理!A:A,0)),"")</f>
-        <v/>
-      </c>
-      <c r="AE189" s="21" t="str" cm="1">
-        <f t="array" ref="AE189">IFERROR(INDEX(商品管理!F:F,MATCH(B189,商品管理!A:A,0)),"")</f>
-        <v/>
-      </c>
-      <c r="AF189" s="21" t="str" cm="1">
-        <f t="array" ref="AF189">IFERROR(INDEX(FBA仓库代码表!G:G,MATCH(E189,FBA仓库代码表!B:B,0)),"")</f>
-        <v/>
-      </c>
-      <c r="AG189" s="21" t="str" cm="1">
-        <f t="array" ref="AG189">IFERROR(INDEX(FBA仓库代码表!H:H,MATCH(E189,FBA仓库代码表!B:B,0)),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="190" spans="30:33">
-      <c r="AD190" s="21" t="str" cm="1">
-        <f t="array" ref="AD190">IFERROR(INDEX(商品管理!E:E,MATCH(B190,商品管理!A:A,0)),"")</f>
-        <v/>
-      </c>
-      <c r="AE190" s="21" t="str" cm="1">
-        <f t="array" ref="AE190">IFERROR(INDEX(商品管理!F:F,MATCH(B190,商品管理!A:A,0)),"")</f>
-        <v/>
-      </c>
-      <c r="AF190" s="21" t="str" cm="1">
-        <f t="array" ref="AF190">IFERROR(INDEX(FBA仓库代码表!G:G,MATCH(E190,FBA仓库代码表!B:B,0)),"")</f>
-        <v/>
-      </c>
-      <c r="AG190" s="21" t="str" cm="1">
-        <f t="array" ref="AG190">IFERROR(INDEX(FBA仓库代码表!H:H,MATCH(E190,FBA仓库代码表!B:B,0)),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="191" spans="30:33">
-      <c r="AD191" s="21" t="str" cm="1">
-        <f t="array" ref="AD191">IFERROR(INDEX(商品管理!E:E,MATCH(B191,商品管理!A:A,0)),"")</f>
-        <v/>
-      </c>
-      <c r="AE191" s="21" t="str" cm="1">
-        <f t="array" ref="AE191">IFERROR(INDEX(商品管理!F:F,MATCH(B191,商品管理!A:A,0)),"")</f>
-        <v/>
-      </c>
-      <c r="AF191" s="21" t="str" cm="1">
-        <f t="array" ref="AF191">IFERROR(INDEX(FBA仓库代码表!G:G,MATCH(E191,FBA仓库代码表!B:B,0)),"")</f>
-        <v/>
-      </c>
-      <c r="AG191" s="21" t="str" cm="1">
-        <f t="array" ref="AG191">IFERROR(INDEX(FBA仓库代码表!H:H,MATCH(E191,FBA仓库代码表!B:B,0)),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="192" spans="30:33">
-      <c r="AD192" s="21" t="str" cm="1">
-        <f t="array" ref="AD192">IFERROR(INDEX(商品管理!E:E,MATCH(B192,商品管理!A:A,0)),"")</f>
-        <v/>
-      </c>
-      <c r="AE192" s="21" t="str" cm="1">
-        <f t="array" ref="AE192">IFERROR(INDEX(商品管理!F:F,MATCH(B192,商品管理!A:A,0)),"")</f>
-        <v/>
-      </c>
-      <c r="AF192" s="21" t="str" cm="1">
-        <f t="array" ref="AF192">IFERROR(INDEX(FBA仓库代码表!G:G,MATCH(E192,FBA仓库代码表!B:B,0)),"")</f>
-        <v/>
-      </c>
-      <c r="AG192" s="21" t="str" cm="1">
-        <f t="array" ref="AG192">IFERROR(INDEX(FBA仓库代码表!H:H,MATCH(E192,FBA仓库代码表!B:B,0)),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="193" spans="30:33">
-      <c r="AD193" s="21" t="str" cm="1">
-        <f t="array" ref="AD193">IFERROR(INDEX(商品管理!E:E,MATCH(B193,商品管理!A:A,0)),"")</f>
-        <v/>
-      </c>
-      <c r="AE193" s="21" t="str" cm="1">
-        <f t="array" ref="AE193">IFERROR(INDEX(商品管理!F:F,MATCH(B193,商品管理!A:A,0)),"")</f>
-        <v/>
-      </c>
-      <c r="AF193" s="21" t="str" cm="1">
-        <f t="array" ref="AF193">IFERROR(INDEX(FBA仓库代码表!G:G,MATCH(E193,FBA仓库代码表!B:B,0)),"")</f>
-        <v/>
-      </c>
-      <c r="AG193" s="21" t="str" cm="1">
-        <f t="array" ref="AG193">IFERROR(INDEX(FBA仓库代码表!H:H,MATCH(E193,FBA仓库代码表!B:B,0)),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="194" spans="30:33">
-      <c r="AD194" s="21" t="str" cm="1">
-        <f t="array" ref="AD194">IFERROR(INDEX(商品管理!E:E,MATCH(B194,商品管理!A:A,0)),"")</f>
-        <v/>
-      </c>
-      <c r="AE194" s="21" t="str" cm="1">
-        <f t="array" ref="AE194">IFERROR(INDEX(商品管理!F:F,MATCH(B194,商品管理!A:A,0)),"")</f>
-        <v/>
-      </c>
-      <c r="AF194" s="21" t="str" cm="1">
-        <f t="array" ref="AF194">IFERROR(INDEX(FBA仓库代码表!G:G,MATCH(E194,FBA仓库代码表!B:B,0)),"")</f>
-        <v/>
-      </c>
-      <c r="AG194" s="21" t="str" cm="1">
-        <f t="array" ref="AG194">IFERROR(INDEX(FBA仓库代码表!H:H,MATCH(E194,FBA仓库代码表!B:B,0)),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="195" spans="30:33">
-      <c r="AD195" s="21" t="str" cm="1">
-        <f t="array" ref="AD195">IFERROR(INDEX(商品管理!E:E,MATCH(B195,商品管理!A:A,0)),"")</f>
-        <v/>
-      </c>
-      <c r="AE195" s="21" t="str" cm="1">
-        <f t="array" ref="AE195">IFERROR(INDEX(商品管理!F:F,MATCH(B195,商品管理!A:A,0)),"")</f>
-        <v/>
-      </c>
-      <c r="AF195" s="21" t="str" cm="1">
-        <f t="array" ref="AF195">IFERROR(INDEX(FBA仓库代码表!G:G,MATCH(E195,FBA仓库代码表!B:B,0)),"")</f>
-        <v/>
-      </c>
-      <c r="AG195" s="21" t="str" cm="1">
-        <f t="array" ref="AG195">IFERROR(INDEX(FBA仓库代码表!H:H,MATCH(E195,FBA仓库代码表!B:B,0)),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="196" spans="30:33">
-      <c r="AD196" s="21" t="str" cm="1">
-        <f t="array" ref="AD196">IFERROR(INDEX(商品管理!E:E,MATCH(B196,商品管理!A:A,0)),"")</f>
-        <v/>
-      </c>
-      <c r="AE196" s="21" t="str" cm="1">
-        <f t="array" ref="AE196">IFERROR(INDEX(商品管理!F:F,MATCH(B196,商品管理!A:A,0)),"")</f>
-        <v/>
-      </c>
-      <c r="AF196" s="21" t="str" cm="1">
-        <f t="array" ref="AF196">IFERROR(INDEX(FBA仓库代码表!G:G,MATCH(E196,FBA仓库代码表!B:B,0)),"")</f>
-        <v/>
-      </c>
-      <c r="AG196" s="21" t="str" cm="1">
-        <f t="array" ref="AG196">IFERROR(INDEX(FBA仓库代码表!H:H,MATCH(E196,FBA仓库代码表!B:B,0)),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="197" spans="30:33">
-      <c r="AD197" s="21" t="str" cm="1">
-        <f t="array" ref="AD197">IFERROR(INDEX(商品管理!E:E,MATCH(B197,商品管理!A:A,0)),"")</f>
-        <v/>
-      </c>
-      <c r="AE197" s="21" t="str" cm="1">
-        <f t="array" ref="AE197">IFERROR(INDEX(商品管理!F:F,MATCH(B197,商品管理!A:A,0)),"")</f>
-        <v/>
-      </c>
-      <c r="AF197" s="21" t="str" cm="1">
-        <f t="array" ref="AF197">IFERROR(INDEX(FBA仓库代码表!G:G,MATCH(E197,FBA仓库代码表!B:B,0)),"")</f>
-        <v/>
-      </c>
-      <c r="AG197" s="21" t="str" cm="1">
-        <f t="array" ref="AG197">IFERROR(INDEX(FBA仓库代码表!H:H,MATCH(E197,FBA仓库代码表!B:B,0)),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="198" spans="30:33">
-      <c r="AD198" s="21" t="str" cm="1">
-        <f t="array" ref="AD198">IFERROR(INDEX(商品管理!E:E,MATCH(B198,商品管理!A:A,0)),"")</f>
-        <v/>
-      </c>
-      <c r="AE198" s="21" t="str" cm="1">
-        <f t="array" ref="AE198">IFERROR(INDEX(商品管理!F:F,MATCH(B198,商品管理!A:A,0)),"")</f>
-        <v/>
-      </c>
-      <c r="AF198" s="21" t="str" cm="1">
-        <f t="array" ref="AF198">IFERROR(INDEX(FBA仓库代码表!G:G,MATCH(E198,FBA仓库代码表!B:B,0)),"")</f>
-        <v/>
-      </c>
-      <c r="AG198" s="21" t="str" cm="1">
-        <f t="array" ref="AG198">IFERROR(INDEX(FBA仓库代码表!H:H,MATCH(E198,FBA仓库代码表!B:B,0)),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="199" spans="30:33">
-      <c r="AD199" s="21" t="str" cm="1">
-        <f t="array" ref="AD199">IFERROR(INDEX(商品管理!E:E,MATCH(B199,商品管理!A:A,0)),"")</f>
-        <v/>
-      </c>
-      <c r="AE199" s="21" t="str" cm="1">
-        <f t="array" ref="AE199">IFERROR(INDEX(商品管理!F:F,MATCH(B199,商品管理!A:A,0)),"")</f>
-        <v/>
-      </c>
-      <c r="AF199" s="21" t="str" cm="1">
-        <f t="array" ref="AF199">IFERROR(INDEX(FBA仓库代码表!G:G,MATCH(E199,FBA仓库代码表!B:B,0)),"")</f>
-        <v/>
-      </c>
-      <c r="AG199" s="21" t="str" cm="1">
-        <f t="array" ref="AG199">IFERROR(INDEX(FBA仓库代码表!H:H,MATCH(E199,FBA仓库代码表!B:B,0)),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="200" spans="30:33">
-      <c r="AD200" s="21" t="str" cm="1">
-        <f t="array" ref="AD200">IFERROR(INDEX(商品管理!E:E,MATCH(B200,商品管理!A:A,0)),"")</f>
-        <v/>
-      </c>
-      <c r="AE200" s="21" t="str" cm="1">
-        <f t="array" ref="AE200">IFERROR(INDEX(商品管理!F:F,MATCH(B200,商品管理!A:A,0)),"")</f>
-        <v/>
-      </c>
-      <c r="AF200" s="21" t="str" cm="1">
-        <f t="array" ref="AF200">IFERROR(INDEX(FBA仓库代码表!G:G,MATCH(E200,FBA仓库代码表!B:B,0)),"")</f>
-        <v/>
-      </c>
-      <c r="AG200" s="21" t="str" cm="1">
-        <f t="array" ref="AG200">IFERROR(INDEX(FBA仓库代码表!H:H,MATCH(E200,FBA仓库代码表!B:B,0)),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="201" spans="30:33">
-      <c r="AD201" s="21" t="str" cm="1">
-        <f t="array" ref="AD201">IFERROR(INDEX(商品管理!E:E,MATCH(B201,商品管理!A:A,0)),"")</f>
-        <v/>
-      </c>
-      <c r="AE201" s="21" t="str" cm="1">
-        <f t="array" ref="AE201">IFERROR(INDEX(商品管理!F:F,MATCH(B201,商品管理!A:A,0)),"")</f>
-        <v/>
-      </c>
-      <c r="AF201" s="21" t="str" cm="1">
-        <f t="array" ref="AF201">IFERROR(INDEX(FBA仓库代码表!G:G,MATCH(E201,FBA仓库代码表!B:B,0)),"")</f>
-        <v/>
-      </c>
-      <c r="AG201" s="21" t="str" cm="1">
-        <f t="array" ref="AG201">IFERROR(INDEX(FBA仓库代码表!H:H,MATCH(E201,FBA仓库代码表!B:B,0)),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="202" spans="30:33">
-      <c r="AD202" s="21" t="str" cm="1">
-        <f t="array" ref="AD202">IFERROR(INDEX(商品管理!E:E,MATCH(B202,商品管理!A:A,0)),"")</f>
-        <v/>
-      </c>
-      <c r="AE202" s="21" t="str" cm="1">
-        <f t="array" ref="AE202">IFERROR(INDEX(商品管理!F:F,MATCH(B202,商品管理!A:A,0)),"")</f>
-        <v/>
-      </c>
-      <c r="AF202" s="21" t="str" cm="1">
-        <f t="array" ref="AF202">IFERROR(INDEX(FBA仓库代码表!G:G,MATCH(E202,FBA仓库代码表!B:B,0)),"")</f>
-        <v/>
-      </c>
-      <c r="AG202" s="21" t="str" cm="1">
-        <f t="array" ref="AG202">IFERROR(INDEX(FBA仓库代码表!H:H,MATCH(E202,FBA仓库代码表!B:B,0)),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="203" spans="30:33">
-      <c r="AD203" s="21" t="str" cm="1">
-        <f t="array" ref="AD203">IFERROR(INDEX(商品管理!E:E,MATCH(B203,商品管理!A:A,0)),"")</f>
-        <v/>
-      </c>
-      <c r="AE203" s="21" t="str" cm="1">
-        <f t="array" ref="AE203">IFERROR(INDEX(商品管理!F:F,MATCH(B203,商品管理!A:A,0)),"")</f>
-        <v/>
-      </c>
-      <c r="AF203" s="21" t="str" cm="1">
-        <f t="array" ref="AF203">IFERROR(INDEX(FBA仓库代码表!G:G,MATCH(E203,FBA仓库代码表!B:B,0)),"")</f>
-        <v/>
-      </c>
-      <c r="AG203" s="21" t="str" cm="1">
-        <f t="array" ref="AG203">IFERROR(INDEX(FBA仓库代码表!H:H,MATCH(E203,FBA仓库代码表!B:B,0)),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="204" spans="30:33">
-      <c r="AD204" s="21" t="str" cm="1">
-        <f t="array" ref="AD204">IFERROR(INDEX(商品管理!E:E,MATCH(B204,商品管理!A:A,0)),"")</f>
-        <v/>
-      </c>
-      <c r="AE204" s="21" t="str" cm="1">
-        <f t="array" ref="AE204">IFERROR(INDEX(商品管理!F:F,MATCH(B204,商品管理!A:A,0)),"")</f>
-        <v/>
-      </c>
-      <c r="AF204" s="21" t="str" cm="1">
-        <f t="array" ref="AF204">IFERROR(INDEX(FBA仓库代码表!G:G,MATCH(E204,FBA仓库代码表!B:B,0)),"")</f>
-        <v/>
-      </c>
-      <c r="AG204" s="21" t="str" cm="1">
-        <f t="array" ref="AG204">IFERROR(INDEX(FBA仓库代码表!H:H,MATCH(E204,FBA仓库代码表!B:B,0)),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="205" spans="30:33">
-      <c r="AD205" s="21" t="str" cm="1">
-        <f t="array" ref="AD205">IFERROR(INDEX(商品管理!E:E,MATCH(B205,商品管理!A:A,0)),"")</f>
-        <v/>
-      </c>
-      <c r="AE205" s="21" t="str" cm="1">
-        <f t="array" ref="AE205">IFERROR(INDEX(商品管理!F:F,MATCH(B205,商品管理!A:A,0)),"")</f>
-        <v/>
-      </c>
-      <c r="AF205" s="21" t="str" cm="1">
-        <f t="array" ref="AF205">IFERROR(INDEX(FBA仓库代码表!G:G,MATCH(E205,FBA仓库代码表!B:B,0)),"")</f>
-        <v/>
-      </c>
-      <c r="AG205" s="21" t="str" cm="1">
-        <f t="array" ref="AG205">IFERROR(INDEX(FBA仓库代码表!H:H,MATCH(E205,FBA仓库代码表!B:B,0)),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="206" spans="30:33">
-      <c r="AD206" s="21" t="str" cm="1">
-        <f t="array" ref="AD206">IFERROR(INDEX(商品管理!E:E,MATCH(B206,商品管理!A:A,0)),"")</f>
-        <v/>
-      </c>
-      <c r="AE206" s="21" t="str" cm="1">
-        <f t="array" ref="AE206">IFERROR(INDEX(商品管理!F:F,MATCH(B206,商品管理!A:A,0)),"")</f>
-        <v/>
-      </c>
-      <c r="AF206" s="21" t="str" cm="1">
-        <f t="array" ref="AF206">IFERROR(INDEX(FBA仓库代码表!G:G,MATCH(E206,FBA仓库代码表!B:B,0)),"")</f>
-        <v/>
-      </c>
-      <c r="AG206" s="21" t="str" cm="1">
-        <f t="array" ref="AG206">IFERROR(INDEX(FBA仓库代码表!H:H,MATCH(E206,FBA仓库代码表!B:B,0)),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="207" spans="30:33">
-      <c r="AD207" s="21" t="str" cm="1">
-        <f t="array" ref="AD207">IFERROR(INDEX(商品管理!E:E,MATCH(B207,商品管理!A:A,0)),"")</f>
-        <v/>
-      </c>
-      <c r="AE207" s="21" t="str" cm="1">
-        <f t="array" ref="AE207">IFERROR(INDEX(商品管理!F:F,MATCH(B207,商品管理!A:A,0)),"")</f>
-        <v/>
-      </c>
-      <c r="AF207" s="21" t="str" cm="1">
-        <f t="array" ref="AF207">IFERROR(INDEX(FBA仓库代码表!G:G,MATCH(E207,FBA仓库代码表!B:B,0)),"")</f>
-        <v/>
-      </c>
-      <c r="AG207" s="21" t="str" cm="1">
-        <f t="array" ref="AG207">IFERROR(INDEX(FBA仓库代码表!H:H,MATCH(E207,FBA仓库代码表!B:B,0)),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="208" spans="30:33">
-      <c r="AD208" s="21" t="str" cm="1">
-        <f t="array" ref="AD208">IFERROR(INDEX(商品管理!E:E,MATCH(B208,商品管理!A:A,0)),"")</f>
-        <v/>
-      </c>
-      <c r="AE208" s="21" t="str" cm="1">
-        <f t="array" ref="AE208">IFERROR(INDEX(商品管理!F:F,MATCH(B208,商品管理!A:A,0)),"")</f>
-        <v/>
-      </c>
-      <c r="AF208" s="21" t="str" cm="1">
-        <f t="array" ref="AF208">IFERROR(INDEX(FBA仓库代码表!G:G,MATCH(E208,FBA仓库代码表!B:B,0)),"")</f>
-        <v/>
-      </c>
-      <c r="AG208" s="21" t="str" cm="1">
-        <f t="array" ref="AG208">IFERROR(INDEX(FBA仓库代码表!H:H,MATCH(E208,FBA仓库代码表!B:B,0)),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="209" spans="30:33">
-      <c r="AD209" s="21" t="str" cm="1">
-        <f t="array" ref="AD209">IFERROR(INDEX(商品管理!E:E,MATCH(B209,商品管理!A:A,0)),"")</f>
-        <v/>
-      </c>
-      <c r="AE209" s="21" t="str" cm="1">
-        <f t="array" ref="AE209">IFERROR(INDEX(商品管理!F:F,MATCH(B209,商品管理!A:A,0)),"")</f>
-        <v/>
-      </c>
-      <c r="AF209" s="21" t="str" cm="1">
-        <f t="array" ref="AF209">IFERROR(INDEX(FBA仓库代码表!G:G,MATCH(E209,FBA仓库代码表!B:B,0)),"")</f>
-        <v/>
-      </c>
-      <c r="AG209" s="21" t="str" cm="1">
-        <f t="array" ref="AG209">IFERROR(INDEX(FBA仓库代码表!H:H,MATCH(E209,FBA仓库代码表!B:B,0)),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="210" spans="30:33">
-      <c r="AD210" s="21" t="str" cm="1">
-        <f t="array" ref="AD210">IFERROR(INDEX(商品管理!E:E,MATCH(B210,商品管理!A:A,0)),"")</f>
-        <v/>
-      </c>
-      <c r="AE210" s="21" t="str" cm="1">
-        <f t="array" ref="AE210">IFERROR(INDEX(商品管理!F:F,MATCH(B210,商品管理!A:A,0)),"")</f>
-        <v/>
-      </c>
-      <c r="AF210" s="21" t="str" cm="1">
-        <f t="array" ref="AF210">IFERROR(INDEX(FBA仓库代码表!G:G,MATCH(E210,FBA仓库代码表!B:B,0)),"")</f>
-        <v/>
-      </c>
-      <c r="AG210" s="21" t="str" cm="1">
-        <f t="array" ref="AG210">IFERROR(INDEX(FBA仓库代码表!H:H,MATCH(E210,FBA仓库代码表!B:B,0)),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="211" spans="30:33">
-      <c r="AD211" s="21" t="str" cm="1">
-        <f t="array" ref="AD211">IFERROR(INDEX(商品管理!E:E,MATCH(B211,商品管理!A:A,0)),"")</f>
-        <v/>
-      </c>
-      <c r="AE211" s="21" t="str" cm="1">
-        <f t="array" ref="AE211">IFERROR(INDEX(商品管理!F:F,MATCH(B211,商品管理!A:A,0)),"")</f>
-        <v/>
-      </c>
-      <c r="AF211" s="21" t="str" cm="1">
-        <f t="array" ref="AF211">IFERROR(INDEX(FBA仓库代码表!G:G,MATCH(E211,FBA仓库代码表!B:B,0)),"")</f>
-        <v/>
-      </c>
-      <c r="AG211" s="21" t="str" cm="1">
-        <f t="array" ref="AG211">IFERROR(INDEX(FBA仓库代码表!H:H,MATCH(E211,FBA仓库代码表!B:B,0)),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="212" spans="30:33">
-      <c r="AD212" s="21" t="str" cm="1">
-        <f t="array" ref="AD212">IFERROR(INDEX(商品管理!E:E,MATCH(B212,商品管理!A:A,0)),"")</f>
-        <v/>
-      </c>
-      <c r="AE212" s="21" t="str" cm="1">
-        <f t="array" ref="AE212">IFERROR(INDEX(商品管理!F:F,MATCH(B212,商品管理!A:A,0)),"")</f>
-        <v/>
-      </c>
-      <c r="AF212" s="21" t="str" cm="1">
-        <f t="array" ref="AF212">IFERROR(INDEX(FBA仓库代码表!G:G,MATCH(E212,FBA仓库代码表!B:B,0)),"")</f>
-        <v/>
-      </c>
-      <c r="AG212" s="21" t="str" cm="1">
-        <f t="array" ref="AG212">IFERROR(INDEX(FBA仓库代码表!H:H,MATCH(E212,FBA仓库代码表!B:B,0)),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="213" spans="30:33">
-      <c r="AD213" s="21" t="str" cm="1">
-        <f t="array" ref="AD213">IFERROR(INDEX(商品管理!E:E,MATCH(B213,商品管理!A:A,0)),"")</f>
-        <v/>
-      </c>
-      <c r="AE213" s="21" t="str" cm="1">
-        <f t="array" ref="AE213">IFERROR(INDEX(商品管理!F:F,MATCH(B213,商品管理!A:A,0)),"")</f>
-        <v/>
-      </c>
-      <c r="AF213" s="21" t="str" cm="1">
-        <f t="array" ref="AF213">IFERROR(INDEX(FBA仓库代码表!G:G,MATCH(E213,FBA仓库代码表!B:B,0)),"")</f>
-        <v/>
-      </c>
-      <c r="AG213" s="21" t="str" cm="1">
-        <f t="array" ref="AG213">IFERROR(INDEX(FBA仓库代码表!H:H,MATCH(E213,FBA仓库代码表!B:B,0)),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="214" spans="30:33">
-      <c r="AD214" s="21" t="str" cm="1">
-        <f t="array" ref="AD214">IFERROR(INDEX(商品管理!E:E,MATCH(B214,商品管理!A:A,0)),"")</f>
-        <v/>
-      </c>
-      <c r="AE214" s="21" t="str" cm="1">
-        <f t="array" ref="AE214">IFERROR(INDEX(商品管理!F:F,MATCH(B214,商品管理!A:A,0)),"")</f>
-        <v/>
-      </c>
-      <c r="AF214" s="21" t="str" cm="1">
-        <f t="array" ref="AF214">IFERROR(INDEX(FBA仓库代码表!G:G,MATCH(E214,FBA仓库代码表!B:B,0)),"")</f>
-        <v/>
-      </c>
-      <c r="AG214" s="21" t="str" cm="1">
-        <f t="array" ref="AG214">IFERROR(INDEX(FBA仓库代码表!H:H,MATCH(E214,FBA仓库代码表!B:B,0)),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="215" spans="30:33">
-      <c r="AD215" s="21" t="str" cm="1">
-        <f t="array" ref="AD215">IFERROR(INDEX(商品管理!E:E,MATCH(B215,商品管理!A:A,0)),"")</f>
-        <v/>
-      </c>
-      <c r="AE215" s="21" t="str" cm="1">
-        <f t="array" ref="AE215">IFERROR(INDEX(商品管理!F:F,MATCH(B215,商品管理!A:A,0)),"")</f>
-        <v/>
-      </c>
-      <c r="AF215" s="21" t="str" cm="1">
-        <f t="array" ref="AF215">IFERROR(INDEX(FBA仓库代码表!G:G,MATCH(E215,FBA仓库代码表!B:B,0)),"")</f>
-        <v/>
-      </c>
-      <c r="AG215" s="21" t="str" cm="1">
-        <f t="array" ref="AG215">IFERROR(INDEX(FBA仓库代码表!H:H,MATCH(E215,FBA仓库代码表!B:B,0)),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="216" spans="30:33">
-      <c r="AD216" s="21" t="str" cm="1">
-        <f t="array" ref="AD216">IFERROR(INDEX(商品管理!E:E,MATCH(B216,商品管理!A:A,0)),"")</f>
-        <v/>
-      </c>
-      <c r="AE216" s="21" t="str" cm="1">
-        <f t="array" ref="AE216">IFERROR(INDEX(商品管理!F:F,MATCH(B216,商品管理!A:A,0)),"")</f>
-        <v/>
-      </c>
-      <c r="AF216" s="21" t="str" cm="1">
-        <f t="array" ref="AF216">IFERROR(INDEX(FBA仓库代码表!G:G,MATCH(E216,FBA仓库代码表!B:B,0)),"")</f>
-        <v/>
-      </c>
-      <c r="AG216" s="21" t="str" cm="1">
-        <f t="array" ref="AG216">IFERROR(INDEX(FBA仓库代码表!H:H,MATCH(E216,FBA仓库代码表!B:B,0)),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="217" spans="30:33">
-      <c r="AD217" s="21" t="str" cm="1">
-        <f t="array" ref="AD217">IFERROR(INDEX(商品管理!E:E,MATCH(B217,商品管理!A:A,0)),"")</f>
-        <v/>
-      </c>
-      <c r="AE217" s="21" t="str" cm="1">
-        <f t="array" ref="AE217">IFERROR(INDEX(商品管理!F:F,MATCH(B217,商品管理!A:A,0)),"")</f>
-        <v/>
-      </c>
-      <c r="AF217" s="21" t="str" cm="1">
-        <f t="array" ref="AF217">IFERROR(INDEX(FBA仓库代码表!G:G,MATCH(E217,FBA仓库代码表!B:B,0)),"")</f>
-        <v/>
-      </c>
-      <c r="AG217" s="21" t="str" cm="1">
-        <f t="array" ref="AG217">IFERROR(INDEX(FBA仓库代码表!H:H,MATCH(E217,FBA仓库代码表!B:B,0)),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="218" spans="30:33">
-      <c r="AD218" s="21" t="str" cm="1">
-        <f t="array" ref="AD218">IFERROR(INDEX(商品管理!E:E,MATCH(B218,商品管理!A:A,0)),"")</f>
-        <v/>
-      </c>
-      <c r="AE218" s="21" t="str" cm="1">
-        <f t="array" ref="AE218">IFERROR(INDEX(商品管理!F:F,MATCH(B218,商品管理!A:A,0)),"")</f>
-        <v/>
-      </c>
-      <c r="AF218" s="21" t="str" cm="1">
-        <f t="array" ref="AF218">IFERROR(INDEX(FBA仓库代码表!G:G,MATCH(E218,FBA仓库代码表!B:B,0)),"")</f>
-        <v/>
-      </c>
-      <c r="AG218" s="21" t="str" cm="1">
-        <f t="array" ref="AG218">IFERROR(INDEX(FBA仓库代码表!H:H,MATCH(E218,FBA仓库代码表!B:B,0)),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="219" spans="30:33">
-      <c r="AD219" s="21" t="str" cm="1">
-        <f t="array" ref="AD219">IFERROR(INDEX(商品管理!E:E,MATCH(B219,商品管理!A:A,0)),"")</f>
-        <v/>
-      </c>
-      <c r="AE219" s="21" t="str" cm="1">
-        <f t="array" ref="AE219">IFERROR(INDEX(商品管理!F:F,MATCH(B219,商品管理!A:A,0)),"")</f>
-        <v/>
-      </c>
-      <c r="AF219" s="21" t="str" cm="1">
-        <f t="array" ref="AF219">IFERROR(INDEX(FBA仓库代码表!G:G,MATCH(E219,FBA仓库代码表!B:B,0)),"")</f>
-        <v/>
-      </c>
-      <c r="AG219" s="21" t="str" cm="1">
-        <f t="array" ref="AG219">IFERROR(INDEX(FBA仓库代码表!H:H,MATCH(E219,FBA仓库代码表!B:B,0)),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="220" spans="30:33">
-      <c r="AD220" s="21" t="str" cm="1">
-        <f t="array" ref="AD220">IFERROR(INDEX(商品管理!E:E,MATCH(B220,商品管理!A:A,0)),"")</f>
-        <v/>
-      </c>
-      <c r="AE220" s="21" t="str" cm="1">
-        <f t="array" ref="AE220">IFERROR(INDEX(商品管理!F:F,MATCH(B220,商品管理!A:A,0)),"")</f>
-        <v/>
-      </c>
-      <c r="AF220" s="21" t="str" cm="1">
-        <f t="array" ref="AF220">IFERROR(INDEX(FBA仓库代码表!G:G,MATCH(E220,FBA仓库代码表!B:B,0)),"")</f>
-        <v/>
-      </c>
-      <c r="AG220" s="21" t="str" cm="1">
-        <f t="array" ref="AG220">IFERROR(INDEX(FBA仓库代码表!H:H,MATCH(E220,FBA仓库代码表!B:B,0)),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="221" spans="30:33">
-      <c r="AD221" s="21" t="str" cm="1">
-        <f t="array" ref="AD221">IFERROR(INDEX(商品管理!E:E,MATCH(B221,商品管理!A:A,0)),"")</f>
-        <v/>
-      </c>
-      <c r="AE221" s="21" t="str" cm="1">
-        <f t="array" ref="AE221">IFERROR(INDEX(商品管理!F:F,MATCH(B221,商品管理!A:A,0)),"")</f>
-        <v/>
-      </c>
-      <c r="AF221" s="21" t="str" cm="1">
-        <f t="array" ref="AF221">IFERROR(INDEX(FBA仓库代码表!G:G,MATCH(E221,FBA仓库代码表!B:B,0)),"")</f>
-        <v/>
-      </c>
-      <c r="AG221" s="21" t="str" cm="1">
-        <f t="array" ref="AG221">IFERROR(INDEX(FBA仓库代码表!H:H,MATCH(E221,FBA仓库代码表!B:B,0)),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="222" spans="30:33">
-      <c r="AD222" s="21" t="str" cm="1">
-        <f t="array" ref="AD222">IFERROR(INDEX(商品管理!E:E,MATCH(B222,商品管理!A:A,0)),"")</f>
-        <v/>
-      </c>
-      <c r="AE222" s="21" t="str" cm="1">
-        <f t="array" ref="AE222">IFERROR(INDEX(商品管理!F:F,MATCH(B222,商品管理!A:A,0)),"")</f>
-        <v/>
-      </c>
-      <c r="AF222" s="21" t="str" cm="1">
-        <f t="array" ref="AF222">IFERROR(INDEX(FBA仓库代码表!G:G,MATCH(E222,FBA仓库代码表!B:B,0)),"")</f>
-        <v/>
-      </c>
-      <c r="AG222" s="21" t="str" cm="1">
-        <f t="array" ref="AG222">IFERROR(INDEX(FBA仓库代码表!H:H,MATCH(E222,FBA仓库代码表!B:B,0)),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="223" spans="30:33">
-      <c r="AD223" s="21" t="str" cm="1">
-        <f t="array" ref="AD223">IFERROR(INDEX(商品管理!E:E,MATCH(B223,商品管理!A:A,0)),"")</f>
-        <v/>
-      </c>
-      <c r="AE223" s="21" t="str" cm="1">
-        <f t="array" ref="AE223">IFERROR(INDEX(商品管理!F:F,MATCH(B223,商品管理!A:A,0)),"")</f>
-        <v/>
-      </c>
-      <c r="AF223" s="21" t="str" cm="1">
-        <f t="array" ref="AF223">IFERROR(INDEX(FBA仓库代码表!G:G,MATCH(E223,FBA仓库代码表!B:B,0)),"")</f>
-        <v/>
-      </c>
-      <c r="AG223" s="21" t="str" cm="1">
-        <f t="array" ref="AG223">IFERROR(INDEX(FBA仓库代码表!H:H,MATCH(E223,FBA仓库代码表!B:B,0)),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="224" spans="30:33">
-      <c r="AD224" s="21" t="str" cm="1">
-        <f t="array" ref="AD224">IFERROR(INDEX(商品管理!E:E,MATCH(B224,商品管理!A:A,0)),"")</f>
-        <v/>
-      </c>
-      <c r="AE224" s="21" t="str" cm="1">
-        <f t="array" ref="AE224">IFERROR(INDEX(商品管理!F:F,MATCH(B224,商品管理!A:A,0)),"")</f>
-        <v/>
-      </c>
-      <c r="AF224" s="21" t="str" cm="1">
-        <f t="array" ref="AF224">IFERROR(INDEX(FBA仓库代码表!G:G,MATCH(E224,FBA仓库代码表!B:B,0)),"")</f>
-        <v/>
-      </c>
-      <c r="AG224" s="21" t="str" cm="1">
-        <f t="array" ref="AG224">IFERROR(INDEX(FBA仓库代码表!H:H,MATCH(E224,FBA仓库代码表!B:B,0)),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="225" spans="30:33">
-      <c r="AD225" s="21" t="str" cm="1">
-        <f t="array" ref="AD225">IFERROR(INDEX(商品管理!E:E,MATCH(B225,商品管理!A:A,0)),"")</f>
-        <v/>
-      </c>
-      <c r="AE225" s="21" t="str" cm="1">
-        <f t="array" ref="AE225">IFERROR(INDEX(商品管理!F:F,MATCH(B225,商品管理!A:A,0)),"")</f>
-        <v/>
-      </c>
-      <c r="AF225" s="21" t="str" cm="1">
-        <f t="array" ref="AF225">IFERROR(INDEX(FBA仓库代码表!G:G,MATCH(E225,FBA仓库代码表!B:B,0)),"")</f>
-        <v/>
-      </c>
-      <c r="AG225" s="21" t="str" cm="1">
-        <f t="array" ref="AG225">IFERROR(INDEX(FBA仓库代码表!H:H,MATCH(E225,FBA仓库代码表!B:B,0)),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="226" spans="30:33">
-      <c r="AD226" s="21" t="str" cm="1">
-        <f t="array" ref="AD226">IFERROR(INDEX(商品管理!E:E,MATCH(B226,商品管理!A:A,0)),"")</f>
-        <v/>
-      </c>
-      <c r="AE226" s="21" t="str" cm="1">
-        <f t="array" ref="AE226">IFERROR(INDEX(商品管理!F:F,MATCH(B226,商品管理!A:A,0)),"")</f>
-        <v/>
-      </c>
-      <c r="AF226" s="21" t="str" cm="1">
-        <f t="array" ref="AF226">IFERROR(INDEX(FBA仓库代码表!G:G,MATCH(E226,FBA仓库代码表!B:B,0)),"")</f>
-        <v/>
-      </c>
-      <c r="AG226" s="21" t="str" cm="1">
-        <f t="array" ref="AG226">IFERROR(INDEX(FBA仓库代码表!H:H,MATCH(E226,FBA仓库代码表!B:B,0)),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="227" spans="30:33">
-      <c r="AD227" s="21" t="str" cm="1">
-        <f t="array" ref="AD227">IFERROR(INDEX(商品管理!E:E,MATCH(B227,商品管理!A:A,0)),"")</f>
-        <v/>
-      </c>
-      <c r="AE227" s="21" t="str" cm="1">
-        <f t="array" ref="AE227">IFERROR(INDEX(商品管理!F:F,MATCH(B227,商品管理!A:A,0)),"")</f>
-        <v/>
-      </c>
-      <c r="AF227" s="21" t="str" cm="1">
-        <f t="array" ref="AF227">IFERROR(INDEX(FBA仓库代码表!G:G,MATCH(E227,FBA仓库代码表!B:B,0)),"")</f>
-        <v/>
-      </c>
-      <c r="AG227" s="21" t="str" cm="1">
-        <f t="array" ref="AG227">IFERROR(INDEX(FBA仓库代码表!H:H,MATCH(E227,FBA仓库代码表!B:B,0)),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="228" spans="30:33">
-      <c r="AD228" s="21" t="str" cm="1">
-        <f t="array" ref="AD228">IFERROR(INDEX(商品管理!E:E,MATCH(B228,商品管理!A:A,0)),"")</f>
-        <v/>
-      </c>
-      <c r="AE228" s="21" t="str" cm="1">
-        <f t="array" ref="AE228">IFERROR(INDEX(商品管理!F:F,MATCH(B228,商品管理!A:A,0)),"")</f>
-        <v/>
-      </c>
-      <c r="AF228" s="21" t="str" cm="1">
-        <f t="array" ref="AF228">IFERROR(INDEX(FBA仓库代码表!G:G,MATCH(E228,FBA仓库代码表!B:B,0)),"")</f>
-        <v/>
-      </c>
-      <c r="AG228" s="21" t="str" cm="1">
-        <f t="array" ref="AG228">IFERROR(INDEX(FBA仓库代码表!H:H,MATCH(E228,FBA仓库代码表!B:B,0)),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="229" spans="30:33">
-      <c r="AD229" s="21" t="str" cm="1">
-        <f t="array" ref="AD229">IFERROR(INDEX(商品管理!E:E,MATCH(B229,商品管理!A:A,0)),"")</f>
-        <v/>
-      </c>
-      <c r="AE229" s="21" t="str" cm="1">
-        <f t="array" ref="AE229">IFERROR(INDEX(商品管理!F:F,MATCH(B229,商品管理!A:A,0)),"")</f>
-        <v/>
-      </c>
-      <c r="AF229" s="21" t="str" cm="1">
-        <f t="array" ref="AF229">IFERROR(INDEX(FBA仓库代码表!G:G,MATCH(E229,FBA仓库代码表!B:B,0)),"")</f>
-        <v/>
-      </c>
-      <c r="AG229" s="21" t="str" cm="1">
-        <f t="array" ref="AG229">IFERROR(INDEX(FBA仓库代码表!H:H,MATCH(E229,FBA仓库代码表!B:B,0)),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="230" spans="30:33">
-      <c r="AD230" s="21" t="str" cm="1">
-        <f t="array" ref="AD230">IFERROR(INDEX(商品管理!E:E,MATCH(B230,商品管理!A:A,0)),"")</f>
-        <v/>
-      </c>
-      <c r="AE230" s="21" t="str" cm="1">
-        <f t="array" ref="AE230">IFERROR(INDEX(商品管理!F:F,MATCH(B230,商品管理!A:A,0)),"")</f>
-        <v/>
-      </c>
-      <c r="AF230" s="21" t="str" cm="1">
-        <f t="array" ref="AF230">IFERROR(INDEX(FBA仓库代码表!G:G,MATCH(E230,FBA仓库代码表!B:B,0)),"")</f>
-        <v/>
-      </c>
-      <c r="AG230" s="21" t="str" cm="1">
-        <f t="array" ref="AG230">IFERROR(INDEX(FBA仓库代码表!H:H,MATCH(E230,FBA仓库代码表!B:B,0)),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="231" spans="30:33">
-      <c r="AD231" s="21" t="str" cm="1">
-        <f t="array" ref="AD231">IFERROR(INDEX(商品管理!E:E,MATCH(B231,商品管理!A:A,0)),"")</f>
-        <v/>
-      </c>
-      <c r="AE231" s="21" t="str" cm="1">
-        <f t="array" ref="AE231">IFERROR(INDEX(商品管理!F:F,MATCH(B231,商品管理!A:A,0)),"")</f>
-        <v/>
-      </c>
-      <c r="AF231" s="21" t="str" cm="1">
-        <f t="array" ref="AF231">IFERROR(INDEX(FBA仓库代码表!G:G,MATCH(E231,FBA仓库代码表!B:B,0)),"")</f>
-        <v/>
-      </c>
-      <c r="AG231" s="21" t="str" cm="1">
-        <f t="array" ref="AG231">IFERROR(INDEX(FBA仓库代码表!H:H,MATCH(E231,FBA仓库代码表!B:B,0)),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="232" spans="30:33">
-      <c r="AD232" s="21" t="str" cm="1">
-        <f t="array" ref="AD232">IFERROR(INDEX(商品管理!E:E,MATCH(B232,商品管理!A:A,0)),"")</f>
-        <v/>
-      </c>
-      <c r="AE232" s="21" t="str" cm="1">
-        <f t="array" ref="AE232">IFERROR(INDEX(商品管理!F:F,MATCH(B232,商品管理!A:A,0)),"")</f>
-        <v/>
-      </c>
-      <c r="AF232" s="21" t="str" cm="1">
-        <f t="array" ref="AF232">IFERROR(INDEX(FBA仓库代码表!G:G,MATCH(E232,FBA仓库代码表!B:B,0)),"")</f>
-        <v/>
-      </c>
-      <c r="AG232" s="21" t="str" cm="1">
-        <f t="array" ref="AG232">IFERROR(INDEX(FBA仓库代码表!H:H,MATCH(E232,FBA仓库代码表!B:B,0)),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="233" spans="30:33">
-      <c r="AD233" s="21" t="str" cm="1">
-        <f t="array" ref="AD233">IFERROR(INDEX(商品管理!E:E,MATCH(B233,商品管理!A:A,0)),"")</f>
-        <v/>
-      </c>
-      <c r="AE233" s="21" t="str" cm="1">
-        <f t="array" ref="AE233">IFERROR(INDEX(商品管理!F:F,MATCH(B233,商品管理!A:A,0)),"")</f>
-        <v/>
-      </c>
-      <c r="AF233" s="21" t="str" cm="1">
-        <f t="array" ref="AF233">IFERROR(INDEX(FBA仓库代码表!G:G,MATCH(E233,FBA仓库代码表!B:B,0)),"")</f>
-        <v/>
-      </c>
-      <c r="AG233" s="21" t="str" cm="1">
-        <f t="array" ref="AG233">IFERROR(INDEX(FBA仓库代码表!H:H,MATCH(E233,FBA仓库代码表!B:B,0)),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="234" spans="30:33">
-      <c r="AD234" s="21" t="str" cm="1">
-        <f t="array" ref="AD234">IFERROR(INDEX(商品管理!E:E,MATCH(B234,商品管理!A:A,0)),"")</f>
-        <v/>
-      </c>
-      <c r="AE234" s="21" t="str" cm="1">
-        <f t="array" ref="AE234">IFERROR(INDEX(商品管理!F:F,MATCH(B234,商品管理!A:A,0)),"")</f>
-        <v/>
-      </c>
-      <c r="AF234" s="21" t="str" cm="1">
-        <f t="array" ref="AF234">IFERROR(INDEX(FBA仓库代码表!G:G,MATCH(E234,FBA仓库代码表!B:B,0)),"")</f>
-        <v/>
-      </c>
-      <c r="AG234" s="21" t="str" cm="1">
-        <f t="array" ref="AG234">IFERROR(INDEX(FBA仓库代码表!H:H,MATCH(E234,FBA仓库代码表!B:B,0)),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="235" spans="30:33">
-      <c r="AD235" s="21" t="str" cm="1">
-        <f t="array" ref="AD235">IFERROR(INDEX(商品管理!E:E,MATCH(B235,商品管理!A:A,0)),"")</f>
-        <v/>
-      </c>
-      <c r="AE235" s="21" t="str" cm="1">
-        <f t="array" ref="AE235">IFERROR(INDEX(商品管理!F:F,MATCH(B235,商品管理!A:A,0)),"")</f>
-        <v/>
-      </c>
-      <c r="AF235" s="21" t="str" cm="1">
-        <f t="array" ref="AF235">IFERROR(INDEX(FBA仓库代码表!G:G,MATCH(E235,FBA仓库代码表!B:B,0)),"")</f>
-        <v/>
-      </c>
-      <c r="AG235" s="21" t="str" cm="1">
-        <f t="array" ref="AG235">IFERROR(INDEX(FBA仓库代码表!H:H,MATCH(E235,FBA仓库代码表!B:B,0)),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="236" spans="30:33">
-      <c r="AD236" s="21" t="str" cm="1">
-        <f t="array" ref="AD236">IFERROR(INDEX(商品管理!E:E,MATCH(B236,商品管理!A:A,0)),"")</f>
-        <v/>
-      </c>
-      <c r="AE236" s="21" t="str" cm="1">
-        <f t="array" ref="AE236">IFERROR(INDEX(商品管理!F:F,MATCH(B236,商品管理!A:A,0)),"")</f>
-        <v/>
-      </c>
-      <c r="AF236" s="21" t="str" cm="1">
-        <f t="array" ref="AF236">IFERROR(INDEX(FBA仓库代码表!G:G,MATCH(E236,FBA仓库代码表!B:B,0)),"")</f>
-        <v/>
-      </c>
-      <c r="AG236" s="21" t="str" cm="1">
-        <f t="array" ref="AG236">IFERROR(INDEX(FBA仓库代码表!H:H,MATCH(E236,FBA仓库代码表!B:B,0)),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="237" spans="30:33">
-      <c r="AD237" s="21" t="str" cm="1">
-        <f t="array" ref="AD237">IFERROR(INDEX(商品管理!E:E,MATCH(B237,商品管理!A:A,0)),"")</f>
-        <v/>
-      </c>
-      <c r="AE237" s="21" t="str" cm="1">
-        <f t="array" ref="AE237">IFERROR(INDEX(商品管理!F:F,MATCH(B237,商品管理!A:A,0)),"")</f>
-        <v/>
-      </c>
-      <c r="AF237" s="21" t="str" cm="1">
-        <f t="array" ref="AF237">IFERROR(INDEX(FBA仓库代码表!G:G,MATCH(E237,FBA仓库代码表!B:B,0)),"")</f>
-        <v/>
-      </c>
-      <c r="AG237" s="21" t="str" cm="1">
-        <f t="array" ref="AG237">IFERROR(INDEX(FBA仓库代码表!H:H,MATCH(E237,FBA仓库代码表!B:B,0)),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="238" spans="30:33">
-      <c r="AD238" s="21" t="str" cm="1">
-        <f t="array" ref="AD238">IFERROR(INDEX(商品管理!E:E,MATCH(B238,商品管理!A:A,0)),"")</f>
-        <v/>
-      </c>
-      <c r="AE238" s="21" t="str" cm="1">
-        <f t="array" ref="AE238">IFERROR(INDEX(商品管理!F:F,MATCH(B238,商品管理!A:A,0)),"")</f>
-        <v/>
-      </c>
-      <c r="AF238" s="21" t="str" cm="1">
-        <f t="array" ref="AF238">IFERROR(INDEX(FBA仓库代码表!G:G,MATCH(E238,FBA仓库代码表!B:B,0)),"")</f>
-        <v/>
-      </c>
-      <c r="AG238" s="21" t="str" cm="1">
-        <f t="array" ref="AG238">IFERROR(INDEX(FBA仓库代码表!H:H,MATCH(E238,FBA仓库代码表!B:B,0)),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="239" spans="30:33">
-      <c r="AD239" s="21" t="str" cm="1">
-        <f t="array" ref="AD239">IFERROR(INDEX(商品管理!E:E,MATCH(B239,商品管理!A:A,0)),"")</f>
-        <v/>
-      </c>
-      <c r="AE239" s="21" t="str" cm="1">
-        <f t="array" ref="AE239">IFERROR(INDEX(商品管理!F:F,MATCH(B239,商品管理!A:A,0)),"")</f>
-        <v/>
-      </c>
-      <c r="AF239" s="21" t="str" cm="1">
-        <f t="array" ref="AF239">IFERROR(INDEX(FBA仓库代码表!G:G,MATCH(E239,FBA仓库代码表!B:B,0)),"")</f>
-        <v/>
-      </c>
-      <c r="AG239" s="21" t="str" cm="1">
-        <f t="array" ref="AG239">IFERROR(INDEX(FBA仓库代码表!H:H,MATCH(E239,FBA仓库代码表!B:B,0)),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="240" spans="30:33">
-      <c r="AD240" s="21" t="str" cm="1">
-        <f t="array" ref="AD240">IFERROR(INDEX(商品管理!E:E,MATCH(B240,商品管理!A:A,0)),"")</f>
-        <v/>
-      </c>
-      <c r="AE240" s="21" t="str" cm="1">
-        <f t="array" ref="AE240">IFERROR(INDEX(商品管理!F:F,MATCH(B240,商品管理!A:A,0)),"")</f>
-        <v/>
-      </c>
-      <c r="AF240" s="21" t="str" cm="1">
-        <f t="array" ref="AF240">IFERROR(INDEX(FBA仓库代码表!G:G,MATCH(E240,FBA仓库代码表!B:B,0)),"")</f>
-        <v/>
-      </c>
-      <c r="AG240" s="21" t="str" cm="1">
-        <f t="array" ref="AG240">IFERROR(INDEX(FBA仓库代码表!H:H,MATCH(E240,FBA仓库代码表!B:B,0)),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="241" spans="30:33">
-      <c r="AD241" s="21" t="str" cm="1">
-        <f t="array" ref="AD241">IFERROR(INDEX(商品管理!E:E,MATCH(B241,商品管理!A:A,0)),"")</f>
-        <v/>
-      </c>
-      <c r="AE241" s="21" t="str" cm="1">
-        <f t="array" ref="AE241">IFERROR(INDEX(商品管理!F:F,MATCH(B241,商品管理!A:A,0)),"")</f>
-        <v/>
-      </c>
-      <c r="AF241" s="21" t="str" cm="1">
-        <f t="array" ref="AF241">IFERROR(INDEX(FBA仓库代码表!G:G,MATCH(E241,FBA仓库代码表!B:B,0)),"")</f>
-        <v/>
-      </c>
-      <c r="AG241" s="21" t="str" cm="1">
-        <f t="array" ref="AG241">IFERROR(INDEX(FBA仓库代码表!H:H,MATCH(E241,FBA仓库代码表!B:B,0)),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="242" spans="30:33">
-      <c r="AD242" s="21" t="str" cm="1">
-        <f t="array" ref="AD242">IFERROR(INDEX(商品管理!E:E,MATCH(B242,商品管理!A:A,0)),"")</f>
-        <v/>
-      </c>
-      <c r="AE242" s="21" t="str" cm="1">
-        <f t="array" ref="AE242">IFERROR(INDEX(商品管理!F:F,MATCH(B242,商品管理!A:A,0)),"")</f>
-        <v/>
-      </c>
-      <c r="AF242" s="21" t="str" cm="1">
-        <f t="array" ref="AF242">IFERROR(INDEX(FBA仓库代码表!G:G,MATCH(E242,FBA仓库代码表!B:B,0)),"")</f>
-        <v/>
-      </c>
-      <c r="AG242" s="21" t="str" cm="1">
-        <f t="array" ref="AG242">IFERROR(INDEX(FBA仓库代码表!H:H,MATCH(E242,FBA仓库代码表!B:B,0)),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="243" spans="30:33">
-      <c r="AD243" s="21" t="str" cm="1">
-        <f t="array" ref="AD243">IFERROR(INDEX(商品管理!E:E,MATCH(B243,商品管理!A:A,0)),"")</f>
-        <v/>
-      </c>
-      <c r="AE243" s="21" t="str" cm="1">
-        <f t="array" ref="AE243">IFERROR(INDEX(商品管理!F:F,MATCH(B243,商品管理!A:A,0)),"")</f>
-        <v/>
-      </c>
-      <c r="AF243" s="21" t="str" cm="1">
-        <f t="array" ref="AF243">IFERROR(INDEX(FBA仓库代码表!G:G,MATCH(E243,FBA仓库代码表!B:B,0)),"")</f>
-        <v/>
-      </c>
-      <c r="AG243" s="21" t="str" cm="1">
-        <f t="array" ref="AG243">IFERROR(INDEX(FBA仓库代码表!H:H,MATCH(E243,FBA仓库代码表!B:B,0)),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="244" spans="30:33">
-      <c r="AD244" s="21" t="str" cm="1">
-        <f t="array" ref="AD244">IFERROR(INDEX(商品管理!E:E,MATCH(B244,商品管理!A:A,0)),"")</f>
-        <v/>
-      </c>
-      <c r="AE244" s="21" t="str" cm="1">
-        <f t="array" ref="AE244">IFERROR(INDEX(商品管理!F:F,MATCH(B244,商品管理!A:A,0)),"")</f>
-        <v/>
-      </c>
-      <c r="AF244" s="21" t="str" cm="1">
-        <f t="array" ref="AF244">IFERROR(INDEX(FBA仓库代码表!G:G,MATCH(E244,FBA仓库代码表!B:B,0)),"")</f>
-        <v/>
-      </c>
-      <c r="AG244" s="21" t="str" cm="1">
-        <f t="array" ref="AG244">IFERROR(INDEX(FBA仓库代码表!H:H,MATCH(E244,FBA仓库代码表!B:B,0)),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="245" spans="30:33">
-      <c r="AD245" s="21" t="str" cm="1">
-        <f t="array" ref="AD245">IFERROR(INDEX(商品管理!E:E,MATCH(B245,商品管理!A:A,0)),"")</f>
-        <v/>
-      </c>
-      <c r="AE245" s="21" t="str" cm="1">
-        <f t="array" ref="AE245">IFERROR(INDEX(商品管理!F:F,MATCH(B245,商品管理!A:A,0)),"")</f>
-        <v/>
-      </c>
-      <c r="AF245" s="21" t="str" cm="1">
-        <f t="array" ref="AF245">IFERROR(INDEX(FBA仓库代码表!G:G,MATCH(E245,FBA仓库代码表!B:B,0)),"")</f>
-        <v/>
-      </c>
-      <c r="AG245" s="21" t="str" cm="1">
-        <f t="array" ref="AG245">IFERROR(INDEX(FBA仓库代码表!H:H,MATCH(E245,FBA仓库代码表!B:B,0)),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="246" spans="30:33">
-      <c r="AD246" s="21" t="str" cm="1">
-        <f t="array" ref="AD246">IFERROR(INDEX(商品管理!E:E,MATCH(B246,商品管理!A:A,0)),"")</f>
-        <v/>
-      </c>
-      <c r="AE246" s="21" t="str" cm="1">
-        <f t="array" ref="AE246">IFERROR(INDEX(商品管理!F:F,MATCH(B246,商品管理!A:A,0)),"")</f>
-        <v/>
-      </c>
-      <c r="AF246" s="21" t="str" cm="1">
-        <f t="array" ref="AF246">IFERROR(INDEX(FBA仓库代码表!G:G,MATCH(E246,FBA仓库代码表!B:B,0)),"")</f>
-        <v/>
-      </c>
-      <c r="AG246" s="21" t="str" cm="1">
-        <f t="array" ref="AG246">IFERROR(INDEX(FBA仓库代码表!H:H,MATCH(E246,FBA仓库代码表!B:B,0)),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="247" spans="30:33">
-      <c r="AD247" s="21" t="str" cm="1">
-        <f t="array" ref="AD247">IFERROR(INDEX(商品管理!E:E,MATCH(B247,商品管理!A:A,0)),"")</f>
-        <v/>
-      </c>
-      <c r="AE247" s="21" t="str" cm="1">
-        <f t="array" ref="AE247">IFERROR(INDEX(商品管理!F:F,MATCH(B247,商品管理!A:A,0)),"")</f>
-        <v/>
-      </c>
-      <c r="AF247" s="21" t="str" cm="1">
-        <f t="array" ref="AF247">IFERROR(INDEX(FBA仓库代码表!G:G,MATCH(E247,FBA仓库代码表!B:B,0)),"")</f>
-        <v/>
-      </c>
-      <c r="AG247" s="21" t="str" cm="1">
-        <f t="array" ref="AG247">IFERROR(INDEX(FBA仓库代码表!H:H,MATCH(E247,FBA仓库代码表!B:B,0)),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="248" spans="30:33">
-      <c r="AD248" s="21" t="str" cm="1">
-        <f t="array" ref="AD248">IFERROR(INDEX(商品管理!E:E,MATCH(B248,商品管理!A:A,0)),"")</f>
-        <v/>
-      </c>
-      <c r="AE248" s="21" t="str" cm="1">
-        <f t="array" ref="AE248">IFERROR(INDEX(商品管理!F:F,MATCH(B248,商品管理!A:A,0)),"")</f>
-        <v/>
-      </c>
-      <c r="AF248" s="21" t="str" cm="1">
-        <f t="array" ref="AF248">IFERROR(INDEX(FBA仓库代码表!G:G,MATCH(E248,FBA仓库代码表!B:B,0)),"")</f>
-        <v/>
-      </c>
-      <c r="AG248" s="21" t="str" cm="1">
-        <f t="array" ref="AG248">IFERROR(INDEX(FBA仓库代码表!H:H,MATCH(E248,FBA仓库代码表!B:B,0)),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="249" spans="30:33">
-      <c r="AD249" s="21" t="str" cm="1">
-        <f t="array" ref="AD249">IFERROR(INDEX(商品管理!E:E,MATCH(B249,商品管理!A:A,0)),"")</f>
-        <v/>
-      </c>
-      <c r="AE249" s="21" t="str" cm="1">
-        <f t="array" ref="AE249">IFERROR(INDEX(商品管理!F:F,MATCH(B249,商品管理!A:A,0)),"")</f>
-        <v/>
-      </c>
-      <c r="AF249" s="21" t="str" cm="1">
-        <f t="array" ref="AF249">IFERROR(INDEX(FBA仓库代码表!G:G,MATCH(E249,FBA仓库代码表!B:B,0)),"")</f>
-        <v/>
-      </c>
-      <c r="AG249" s="21" t="str" cm="1">
-        <f t="array" ref="AG249">IFERROR(INDEX(FBA仓库代码表!H:H,MATCH(E249,FBA仓库代码表!B:B,0)),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="250" spans="30:33">
-      <c r="AD250" s="21" t="str" cm="1">
-        <f t="array" ref="AD250">IFERROR(INDEX(商品管理!E:E,MATCH(B250,商品管理!A:A,0)),"")</f>
-        <v/>
-      </c>
-      <c r="AE250" s="21" t="str" cm="1">
-        <f t="array" ref="AE250">IFERROR(INDEX(商品管理!F:F,MATCH(B250,商品管理!A:A,0)),"")</f>
-        <v/>
-      </c>
-      <c r="AF250" s="21" t="str" cm="1">
-        <f t="array" ref="AF250">IFERROR(INDEX(FBA仓库代码表!G:G,MATCH(E250,FBA仓库代码表!B:B,0)),"")</f>
-        <v/>
-      </c>
-      <c r="AG250" s="21" t="str" cm="1">
-        <f t="array" ref="AG250">IFERROR(INDEX(FBA仓库代码表!H:H,MATCH(E250,FBA仓库代码表!B:B,0)),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="251" spans="30:33">
-      <c r="AD251" s="21" t="str" cm="1">
-        <f t="array" ref="AD251">IFERROR(INDEX(商品管理!E:E,MATCH(B251,商品管理!A:A,0)),"")</f>
-        <v/>
-      </c>
-      <c r="AE251" s="21" t="str" cm="1">
-        <f t="array" ref="AE251">IFERROR(INDEX(商品管理!F:F,MATCH(B251,商品管理!A:A,0)),"")</f>
-        <v/>
-      </c>
-      <c r="AF251" s="21" t="str" cm="1">
-        <f t="array" ref="AF251">IFERROR(INDEX(FBA仓库代码表!G:G,MATCH(E251,FBA仓库代码表!B:B,0)),"")</f>
-        <v/>
-      </c>
-      <c r="AG251" s="21" t="str" cm="1">
-        <f t="array" ref="AG251">IFERROR(INDEX(FBA仓库代码表!H:H,MATCH(E251,FBA仓库代码表!B:B,0)),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="252" spans="30:33">
-      <c r="AD252" s="21" t="str" cm="1">
-        <f t="array" ref="AD252">IFERROR(INDEX(商品管理!E:E,MATCH(B252,商品管理!A:A,0)),"")</f>
-        <v/>
-      </c>
-      <c r="AE252" s="21" t="str" cm="1">
-        <f t="array" ref="AE252">IFERROR(INDEX(商品管理!F:F,MATCH(B252,商品管理!A:A,0)),"")</f>
-        <v/>
-      </c>
-      <c r="AF252" s="21" t="str" cm="1">
-        <f t="array" ref="AF252">IFERROR(INDEX(FBA仓库代码表!G:G,MATCH(E252,FBA仓库代码表!B:B,0)),"")</f>
-        <v/>
-      </c>
-      <c r="AG252" s="21" t="str" cm="1">
-        <f t="array" ref="AG252">IFERROR(INDEX(FBA仓库代码表!H:H,MATCH(E252,FBA仓库代码表!B:B,0)),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="253" spans="30:33">
-      <c r="AD253" s="21" t="str" cm="1">
-        <f t="array" ref="AD253">IFERROR(INDEX(商品管理!E:E,MATCH(B253,商品管理!A:A,0)),"")</f>
-        <v/>
-      </c>
-      <c r="AE253" s="21" t="str" cm="1">
-        <f t="array" ref="AE253">IFERROR(INDEX(商品管理!F:F,MATCH(B253,商品管理!A:A,0)),"")</f>
-        <v/>
-      </c>
-      <c r="AF253" s="21" t="str" cm="1">
-        <f t="array" ref="AF253">IFERROR(INDEX(FBA仓库代码表!G:G,MATCH(E253,FBA仓库代码表!B:B,0)),"")</f>
-        <v/>
-      </c>
-      <c r="AG253" s="21" t="str" cm="1">
-        <f t="array" ref="AG253">IFERROR(INDEX(FBA仓库代码表!H:H,MATCH(E253,FBA仓库代码表!B:B,0)),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="254" spans="30:33">
-      <c r="AD254" s="21" t="str" cm="1">
-        <f t="array" ref="AD254">IFERROR(INDEX(商品管理!E:E,MATCH(B254,商品管理!A:A,0)),"")</f>
-        <v/>
-      </c>
-      <c r="AE254" s="21" t="str" cm="1">
-        <f t="array" ref="AE254">IFERROR(INDEX(商品管理!F:F,MATCH(B254,商品管理!A:A,0)),"")</f>
-        <v/>
-      </c>
-      <c r="AF254" s="21" t="str" cm="1">
-        <f t="array" ref="AF254">IFERROR(INDEX(FBA仓库代码表!G:G,MATCH(E254,FBA仓库代码表!B:B,0)),"")</f>
-        <v/>
-      </c>
-      <c r="AG254" s="21" t="str" cm="1">
-        <f t="array" ref="AG254">IFERROR(INDEX(FBA仓库代码表!H:H,MATCH(E254,FBA仓库代码表!B:B,0)),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="255" spans="30:33">
-      <c r="AD255" s="21" t="str" cm="1">
-        <f t="array" ref="AD255">IFERROR(INDEX(商品管理!E:E,MATCH(B255,商品管理!A:A,0)),"")</f>
-        <v/>
-      </c>
-      <c r="AE255" s="21" t="str" cm="1">
-        <f t="array" ref="AE255">IFERROR(INDEX(商品管理!F:F,MATCH(B255,商品管理!A:A,0)),"")</f>
-        <v/>
-      </c>
-      <c r="AF255" s="21" t="str" cm="1">
-        <f t="array" ref="AF255">IFERROR(INDEX(FBA仓库代码表!G:G,MATCH(E255,FBA仓库代码表!B:B,0)),"")</f>
-        <v/>
-      </c>
-      <c r="AG255" s="21" t="str" cm="1">
-        <f t="array" ref="AG255">IFERROR(INDEX(FBA仓库代码表!H:H,MATCH(E255,FBA仓库代码表!B:B,0)),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="256" spans="30:33">
-      <c r="AD256" s="21" t="str" cm="1">
-        <f t="array" ref="AD256">IFERROR(INDEX(商品管理!E:E,MATCH(B256,商品管理!A:A,0)),"")</f>
-        <v/>
-      </c>
-      <c r="AE256" s="21" t="str" cm="1">
-        <f t="array" ref="AE256">IFERROR(INDEX(商品管理!F:F,MATCH(B256,商品管理!A:A,0)),"")</f>
-        <v/>
-      </c>
-      <c r="AF256" s="21" t="str" cm="1">
-        <f t="array" ref="AF256">IFERROR(INDEX(FBA仓库代码表!G:G,MATCH(E256,FBA仓库代码表!B:B,0)),"")</f>
-        <v/>
-      </c>
-      <c r="AG256" s="21" t="str" cm="1">
-        <f t="array" ref="AG256">IFERROR(INDEX(FBA仓库代码表!H:H,MATCH(E256,FBA仓库代码表!B:B,0)),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="257" spans="30:33">
-      <c r="AD257" s="21" t="str" cm="1">
-        <f t="array" ref="AD257">IFERROR(INDEX(商品管理!E:E,MATCH(B257,商品管理!A:A,0)),"")</f>
-        <v/>
-      </c>
-      <c r="AE257" s="21" t="str" cm="1">
-        <f t="array" ref="AE257">IFERROR(INDEX(商品管理!F:F,MATCH(B257,商品管理!A:A,0)),"")</f>
-        <v/>
-      </c>
-      <c r="AF257" s="21" t="str" cm="1">
-        <f t="array" ref="AF257">IFERROR(INDEX(FBA仓库代码表!G:G,MATCH(E257,FBA仓库代码表!B:B,0)),"")</f>
-        <v/>
-      </c>
-      <c r="AG257" s="21" t="str" cm="1">
-        <f t="array" ref="AG257">IFERROR(INDEX(FBA仓库代码表!H:H,MATCH(E257,FBA仓库代码表!B:B,0)),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="258" spans="30:33">
-      <c r="AD258" s="21" t="str" cm="1">
-        <f t="array" ref="AD258">IFERROR(INDEX(商品管理!E:E,MATCH(B258,商品管理!A:A,0)),"")</f>
-        <v/>
-      </c>
-      <c r="AE258" s="21" t="str" cm="1">
-        <f t="array" ref="AE258">IFERROR(INDEX(商品管理!F:F,MATCH(B258,商品管理!A:A,0)),"")</f>
-        <v/>
-      </c>
-      <c r="AF258" s="21" t="str" cm="1">
-        <f t="array" ref="AF258">IFERROR(INDEX(FBA仓库代码表!G:G,MATCH(E258,FBA仓库代码表!B:B,0)),"")</f>
-        <v/>
-      </c>
-      <c r="AG258" s="21" t="str" cm="1">
-        <f t="array" ref="AG258">IFERROR(INDEX(FBA仓库代码表!H:H,MATCH(E258,FBA仓库代码表!B:B,0)),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="259" spans="30:33">
-      <c r="AD259" s="21" t="str" cm="1">
-        <f t="array" ref="AD259">IFERROR(INDEX(商品管理!E:E,MATCH(B259,商品管理!A:A,0)),"")</f>
-        <v/>
-      </c>
-      <c r="AE259" s="21" t="str" cm="1">
-        <f t="array" ref="AE259">IFERROR(INDEX(商品管理!F:F,MATCH(B259,商品管理!A:A,0)),"")</f>
-        <v/>
-      </c>
-      <c r="AF259" s="21" t="str" cm="1">
-        <f t="array" ref="AF259">IFERROR(INDEX(FBA仓库代码表!G:G,MATCH(E259,FBA仓库代码表!B:B,0)),"")</f>
-        <v/>
-      </c>
-      <c r="AG259" s="21" t="str" cm="1">
-        <f t="array" ref="AG259">IFERROR(INDEX(FBA仓库代码表!H:H,MATCH(E259,FBA仓库代码表!B:B,0)),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="260" spans="30:33">
-      <c r="AD260" s="21" t="str" cm="1">
-        <f t="array" ref="AD260">IFERROR(INDEX(商品管理!E:E,MATCH(B260,商品管理!A:A,0)),"")</f>
-        <v/>
-      </c>
-      <c r="AE260" s="21" t="str" cm="1">
-        <f t="array" ref="AE260">IFERROR(INDEX(商品管理!F:F,MATCH(B260,商品管理!A:A,0)),"")</f>
-        <v/>
-      </c>
-      <c r="AF260" s="21" t="str" cm="1">
-        <f t="array" ref="AF260">IFERROR(INDEX(FBA仓库代码表!G:G,MATCH(E260,FBA仓库代码表!B:B,0)),"")</f>
-        <v/>
-      </c>
-      <c r="AG260" s="21" t="str" cm="1">
-        <f t="array" ref="AG260">IFERROR(INDEX(FBA仓库代码表!H:H,MATCH(E260,FBA仓库代码表!B:B,0)),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="261" spans="30:33">
-      <c r="AD261" s="21" t="str" cm="1">
-        <f t="array" ref="AD261">IFERROR(INDEX(商品管理!E:E,MATCH(B261,商品管理!A:A,0)),"")</f>
-        <v/>
-      </c>
-      <c r="AE261" s="21" t="str" cm="1">
-        <f t="array" ref="AE261">IFERROR(INDEX(商品管理!F:F,MATCH(B261,商品管理!A:A,0)),"")</f>
-        <v/>
-      </c>
-      <c r="AF261" s="21" t="str" cm="1">
-        <f t="array" ref="AF261">IFERROR(INDEX(FBA仓库代码表!G:G,MATCH(E261,FBA仓库代码表!B:B,0)),"")</f>
-        <v/>
-      </c>
-      <c r="AG261" s="21" t="str" cm="1">
-        <f t="array" ref="AG261">IFERROR(INDEX(FBA仓库代码表!H:H,MATCH(E261,FBA仓库代码表!B:B,0)),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="262" spans="30:33">
-      <c r="AD262" s="21" t="str" cm="1">
-        <f t="array" ref="AD262">IFERROR(INDEX(商品管理!E:E,MATCH(B262,商品管理!A:A,0)),"")</f>
-        <v/>
-      </c>
-      <c r="AE262" s="21" t="str" cm="1">
-        <f t="array" ref="AE262">IFERROR(INDEX(商品管理!F:F,MATCH(B262,商品管理!A:A,0)),"")</f>
-        <v/>
-      </c>
-      <c r="AF262" s="21" t="str" cm="1">
-        <f t="array" ref="AF262">IFERROR(INDEX(FBA仓库代码表!G:G,MATCH(E262,FBA仓库代码表!B:B,0)),"")</f>
-        <v/>
-      </c>
-      <c r="AG262" s="21" t="str" cm="1">
-        <f t="array" ref="AG262">IFERROR(INDEX(FBA仓库代码表!H:H,MATCH(E262,FBA仓库代码表!B:B,0)),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="263" spans="30:33">
-      <c r="AD263" s="21" t="str" cm="1">
-        <f t="array" ref="AD263">IFERROR(INDEX(商品管理!E:E,MATCH(B263,商品管理!A:A,0)),"")</f>
-        <v/>
-      </c>
-      <c r="AE263" s="21" t="str" cm="1">
-        <f t="array" ref="AE263">IFERROR(INDEX(商品管理!F:F,MATCH(B263,商品管理!A:A,0)),"")</f>
-        <v/>
-      </c>
-      <c r="AF263" s="21" t="str" cm="1">
-        <f t="array" ref="AF263">IFERROR(INDEX(FBA仓库代码表!G:G,MATCH(E263,FBA仓库代码表!B:B,0)),"")</f>
-        <v/>
-      </c>
-      <c r="AG263" s="21" t="str" cm="1">
-        <f t="array" ref="AG263">IFERROR(INDEX(FBA仓库代码表!H:H,MATCH(E263,FBA仓库代码表!B:B,0)),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="264" spans="30:33">
-      <c r="AD264" s="21" t="str" cm="1">
-        <f t="array" ref="AD264">IFERROR(INDEX(商品管理!E:E,MATCH(B264,商品管理!A:A,0)),"")</f>
-        <v/>
-      </c>
-      <c r="AE264" s="21" t="str" cm="1">
-        <f t="array" ref="AE264">IFERROR(INDEX(商品管理!F:F,MATCH(B264,商品管理!A:A,0)),"")</f>
-        <v/>
-      </c>
-      <c r="AF264" s="21" t="str" cm="1">
-        <f t="array" ref="AF264">IFERROR(INDEX(FBA仓库代码表!G:G,MATCH(E264,FBA仓库代码表!B:B,0)),"")</f>
-        <v/>
-      </c>
-      <c r="AG264" s="21" t="str" cm="1">
-        <f t="array" ref="AG264">IFERROR(INDEX(FBA仓库代码表!H:H,MATCH(E264,FBA仓库代码表!B:B,0)),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="265" spans="30:33">
-      <c r="AD265" s="21" t="str" cm="1">
-        <f t="array" ref="AD265">IFERROR(INDEX(商品管理!E:E,MATCH(B265,商品管理!A:A,0)),"")</f>
-        <v/>
-      </c>
-      <c r="AE265" s="21" t="str" cm="1">
-        <f t="array" ref="AE265">IFERROR(INDEX(商品管理!F:F,MATCH(B265,商品管理!A:A,0)),"")</f>
-        <v/>
-      </c>
-      <c r="AF265" s="21" t="str" cm="1">
-        <f t="array" ref="AF265">IFERROR(INDEX(FBA仓库代码表!G:G,MATCH(E265,FBA仓库代码表!B:B,0)),"")</f>
-        <v/>
-      </c>
-      <c r="AG265" s="21" t="str" cm="1">
-        <f t="array" ref="AG265">IFERROR(INDEX(FBA仓库代码表!H:H,MATCH(E265,FBA仓库代码表!B:B,0)),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="266" spans="30:33">
-      <c r="AD266" s="21" t="str" cm="1">
-        <f t="array" ref="AD266">IFERROR(INDEX(商品管理!E:E,MATCH(B266,商品管理!A:A,0)),"")</f>
-        <v/>
-      </c>
-      <c r="AE266" s="21" t="str" cm="1">
-        <f t="array" ref="AE266">IFERROR(INDEX(商品管理!F:F,MATCH(B266,商品管理!A:A,0)),"")</f>
-        <v/>
-      </c>
-      <c r="AF266" s="21" t="str" cm="1">
-        <f t="array" ref="AF266">IFERROR(INDEX(FBA仓库代码表!G:G,MATCH(E266,FBA仓库代码表!B:B,0)),"")</f>
-        <v/>
-      </c>
-      <c r="AG266" s="21" t="str" cm="1">
-        <f t="array" ref="AG266">IFERROR(INDEX(FBA仓库代码表!H:H,MATCH(E266,FBA仓库代码表!B:B,0)),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="267" spans="30:33">
-      <c r="AD267" s="21" t="str" cm="1">
-        <f t="array" ref="AD267">IFERROR(INDEX(商品管理!E:E,MATCH(B267,商品管理!A:A,0)),"")</f>
-        <v/>
-      </c>
-      <c r="AE267" s="21" t="str" cm="1">
-        <f t="array" ref="AE267">IFERROR(INDEX(商品管理!F:F,MATCH(B267,商品管理!A:A,0)),"")</f>
-        <v/>
-      </c>
-      <c r="AF267" s="21" t="str" cm="1">
-        <f t="array" ref="AF267">IFERROR(INDEX(FBA仓库代码表!G:G,MATCH(E267,FBA仓库代码表!B:B,0)),"")</f>
-        <v/>
-      </c>
-      <c r="AG267" s="21" t="str" cm="1">
-        <f t="array" ref="AG267">IFERROR(INDEX(FBA仓库代码表!H:H,MATCH(E267,FBA仓库代码表!B:B,0)),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="268" spans="30:33">
-      <c r="AD268" s="21" t="str" cm="1">
-        <f t="array" ref="AD268">IFERROR(INDEX(商品管理!E:E,MATCH(B268,商品管理!A:A,0)),"")</f>
-        <v/>
-      </c>
-      <c r="AE268" s="21" t="str" cm="1">
-        <f t="array" ref="AE268">IFERROR(INDEX(商品管理!F:F,MATCH(B268,商品管理!A:A,0)),"")</f>
-        <v/>
-      </c>
-      <c r="AF268" s="21" t="str" cm="1">
-        <f t="array" ref="AF268">IFERROR(INDEX(FBA仓库代码表!G:G,MATCH(E268,FBA仓库代码表!B:B,0)),"")</f>
-        <v/>
-      </c>
-      <c r="AG268" s="21" t="str" cm="1">
-        <f t="array" ref="AG268">IFERROR(INDEX(FBA仓库代码表!H:H,MATCH(E268,FBA仓库代码表!B:B,0)),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="269" spans="30:33">
-      <c r="AD269" s="21" t="str" cm="1">
-        <f t="array" ref="AD269">IFERROR(INDEX(商品管理!E:E,MATCH(B269,商品管理!A:A,0)),"")</f>
-        <v/>
-      </c>
-      <c r="AE269" s="21" t="str" cm="1">
-        <f t="array" ref="AE269">IFERROR(INDEX(商品管理!F:F,MATCH(B269,商品管理!A:A,0)),"")</f>
-        <v/>
-      </c>
-      <c r="AF269" s="21" t="str" cm="1">
-        <f t="array" ref="AF269">IFERROR(INDEX(FBA仓库代码表!G:G,MATCH(E269,FBA仓库代码表!B:B,0)),"")</f>
-        <v/>
-      </c>
-      <c r="AG269" s="21" t="str" cm="1">
-        <f t="array" ref="AG269">IFERROR(INDEX(FBA仓库代码表!H:H,MATCH(E269,FBA仓库代码表!B:B,0)),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="270" spans="30:33">
-      <c r="AD270" s="21" t="str" cm="1">
-        <f t="array" ref="AD270">IFERROR(INDEX(商品管理!E:E,MATCH(B270,商品管理!A:A,0)),"")</f>
-        <v/>
-      </c>
-      <c r="AE270" s="21" t="str" cm="1">
-        <f t="array" ref="AE270">IFERROR(INDEX(商品管理!F:F,MATCH(B270,商品管理!A:A,0)),"")</f>
-        <v/>
-      </c>
-      <c r="AF270" s="21" t="str" cm="1">
-        <f t="array" ref="AF270">IFERROR(INDEX(FBA仓库代码表!G:G,MATCH(E270,FBA仓库代码表!B:B,0)),"")</f>
-        <v/>
-      </c>
-      <c r="AG270" s="21" t="str" cm="1">
-        <f t="array" ref="AG270">IFERROR(INDEX(FBA仓库代码表!H:H,MATCH(E270,FBA仓库代码表!B:B,0)),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="271" spans="30:33">
-      <c r="AD271" s="21" t="str" cm="1">
-        <f t="array" ref="AD271">IFERROR(INDEX(商品管理!E:E,MATCH(B271,商品管理!A:A,0)),"")</f>
-        <v/>
-      </c>
-      <c r="AE271" s="21" t="str" cm="1">
-        <f t="array" ref="AE271">IFERROR(INDEX(商品管理!F:F,MATCH(B271,商品管理!A:A,0)),"")</f>
-        <v/>
-      </c>
-      <c r="AF271" s="21" t="str" cm="1">
-        <f t="array" ref="AF271">IFERROR(INDEX(FBA仓库代码表!G:G,MATCH(E271,FBA仓库代码表!B:B,0)),"")</f>
-        <v/>
-      </c>
-      <c r="AG271" s="21" t="str" cm="1">
-        <f t="array" ref="AG271">IFERROR(INDEX(FBA仓库代码表!H:H,MATCH(E271,FBA仓库代码表!B:B,0)),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="272" spans="30:33">
-      <c r="AD272" s="21" t="str" cm="1">
-        <f t="array" ref="AD272">IFERROR(INDEX(商品管理!E:E,MATCH(B272,商品管理!A:A,0)),"")</f>
-        <v/>
-      </c>
-      <c r="AE272" s="21" t="str" cm="1">
-        <f t="array" ref="AE272">IFERROR(INDEX(商品管理!F:F,MATCH(B272,商品管理!A:A,0)),"")</f>
-        <v/>
-      </c>
-      <c r="AF272" s="21" t="str" cm="1">
-        <f t="array" ref="AF272">IFERROR(INDEX(FBA仓库代码表!G:G,MATCH(E272,FBA仓库代码表!B:B,0)),"")</f>
-        <v/>
-      </c>
-      <c r="AG272" s="21" t="str" cm="1">
-        <f t="array" ref="AG272">IFERROR(INDEX(FBA仓库代码表!H:H,MATCH(E272,FBA仓库代码表!B:B,0)),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="273" spans="30:33">
-      <c r="AD273" s="21" t="str" cm="1">
-        <f t="array" ref="AD273">IFERROR(INDEX(商品管理!E:E,MATCH(B273,商品管理!A:A,0)),"")</f>
-        <v/>
-      </c>
-      <c r="AE273" s="21" t="str" cm="1">
-        <f t="array" ref="AE273">IFERROR(INDEX(商品管理!F:F,MATCH(B273,商品管理!A:A,0)),"")</f>
-        <v/>
-      </c>
-      <c r="AF273" s="21" t="str" cm="1">
-        <f t="array" ref="AF273">IFERROR(INDEX(FBA仓库代码表!G:G,MATCH(E273,FBA仓库代码表!B:B,0)),"")</f>
-        <v/>
-      </c>
-      <c r="AG273" s="21" t="str" cm="1">
-        <f t="array" ref="AG273">IFERROR(INDEX(FBA仓库代码表!H:H,MATCH(E273,FBA仓库代码表!B:B,0)),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="274" spans="30:33">
-      <c r="AD274" s="21" t="str" cm="1">
-        <f t="array" ref="AD274">IFERROR(INDEX(商品管理!E:E,MATCH(B274,商品管理!A:A,0)),"")</f>
-        <v/>
-      </c>
-      <c r="AE274" s="21" t="str" cm="1">
-        <f t="array" ref="AE274">IFERROR(INDEX(商品管理!F:F,MATCH(B274,商品管理!A:A,0)),"")</f>
-        <v/>
-      </c>
-      <c r="AF274" s="21" t="str" cm="1">
-        <f t="array" ref="AF274">IFERROR(INDEX(FBA仓库代码表!G:G,MATCH(E274,FBA仓库代码表!B:B,0)),"")</f>
-        <v/>
-      </c>
-      <c r="AG274" s="21" t="str" cm="1">
-        <f t="array" ref="AG274">IFERROR(INDEX(FBA仓库代码表!H:H,MATCH(E274,FBA仓库代码表!B:B,0)),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="275" spans="30:33">
-      <c r="AD275" s="21" t="str" cm="1">
-        <f t="array" ref="AD275">IFERROR(INDEX(商品管理!E:E,MATCH(B275,商品管理!A:A,0)),"")</f>
-        <v/>
-      </c>
-      <c r="AE275" s="21" t="str" cm="1">
-        <f t="array" ref="AE275">IFERROR(INDEX(商品管理!F:F,MATCH(B275,商品管理!A:A,0)),"")</f>
-        <v/>
-      </c>
-      <c r="AF275" s="21" t="str" cm="1">
-        <f t="array" ref="AF275">IFERROR(INDEX(FBA仓库代码表!G:G,MATCH(E275,FBA仓库代码表!B:B,0)),"")</f>
-        <v/>
-      </c>
-      <c r="AG275" s="21" t="str" cm="1">
-        <f t="array" ref="AG275">IFERROR(INDEX(FBA仓库代码表!H:H,MATCH(E275,FBA仓库代码表!B:B,0)),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="276" spans="30:33">
-      <c r="AD276" s="21" t="str" cm="1">
-        <f t="array" ref="AD276">IFERROR(INDEX(商品管理!E:E,MATCH(B276,商品管理!A:A,0)),"")</f>
-        <v/>
-      </c>
-      <c r="AE276" s="21" t="str" cm="1">
-        <f t="array" ref="AE276">IFERROR(INDEX(商品管理!F:F,MATCH(B276,商品管理!A:A,0)),"")</f>
-        <v/>
-      </c>
-      <c r="AF276" s="21" t="str" cm="1">
-        <f t="array" ref="AF276">IFERROR(INDEX(FBA仓库代码表!G:G,MATCH(E276,FBA仓库代码表!B:B,0)),"")</f>
-        <v/>
-      </c>
-      <c r="AG276" s="21" t="str" cm="1">
-        <f t="array" ref="AG276">IFERROR(INDEX(FBA仓库代码表!H:H,MATCH(E276,FBA仓库代码表!B:B,0)),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="277" spans="30:33">
-      <c r="AD277" s="21" t="str" cm="1">
-        <f t="array" ref="AD277">IFERROR(INDEX(商品管理!E:E,MATCH(B277,商品管理!A:A,0)),"")</f>
-        <v/>
-      </c>
-      <c r="AE277" s="21" t="str" cm="1">
-        <f t="array" ref="AE277">IFERROR(INDEX(商品管理!F:F,MATCH(B277,商品管理!A:A,0)),"")</f>
-        <v/>
-      </c>
-      <c r="AF277" s="21" t="str" cm="1">
-        <f t="array" ref="AF277">IFERROR(INDEX(FBA仓库代码表!G:G,MATCH(E277,FBA仓库代码表!B:B,0)),"")</f>
-        <v/>
-      </c>
-      <c r="AG277" s="21" t="str" cm="1">
-        <f t="array" ref="AG277">IFERROR(INDEX(FBA仓库代码表!H:H,MATCH(E277,FBA仓库代码表!B:B,0)),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="278" spans="30:33">
-      <c r="AD278" s="21" t="str" cm="1">
-        <f t="array" ref="AD278">IFERROR(INDEX(商品管理!E:E,MATCH(B278,商品管理!A:A,0)),"")</f>
-        <v/>
-      </c>
-      <c r="AE278" s="21" t="str" cm="1">
-        <f t="array" ref="AE278">IFERROR(INDEX(商品管理!F:F,MATCH(B278,商品管理!A:A,0)),"")</f>
-        <v/>
-      </c>
-      <c r="AF278" s="21" t="str" cm="1">
-        <f t="array" ref="AF278">IFERROR(INDEX(FBA仓库代码表!G:G,MATCH(E278,FBA仓库代码表!B:B,0)),"")</f>
-        <v/>
-      </c>
-      <c r="AG278" s="21" t="str" cm="1">
-        <f t="array" ref="AG278">IFERROR(INDEX(FBA仓库代码表!H:H,MATCH(E278,FBA仓库代码表!B:B,0)),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="279" spans="30:33">
-      <c r="AD279" s="21" t="str" cm="1">
-        <f t="array" ref="AD279">IFERROR(INDEX(商品管理!E:E,MATCH(B279,商品管理!A:A,0)),"")</f>
-        <v/>
-      </c>
-      <c r="AE279" s="21" t="str" cm="1">
-        <f t="array" ref="AE279">IFERROR(INDEX(商品管理!F:F,MATCH(B279,商品管理!A:A,0)),"")</f>
-        <v/>
-      </c>
-      <c r="AF279" s="21" t="str" cm="1">
-        <f t="array" ref="AF279">IFERROR(INDEX(FBA仓库代码表!G:G,MATCH(E279,FBA仓库代码表!B:B,0)),"")</f>
-        <v/>
-      </c>
-      <c r="AG279" s="21" t="str" cm="1">
-        <f t="array" ref="AG279">IFERROR(INDEX(FBA仓库代码表!H:H,MATCH(E279,FBA仓库代码表!B:B,0)),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="280" spans="30:33">
-      <c r="AD280" s="21" t="str" cm="1">
-        <f t="array" ref="AD280">IFERROR(INDEX(商品管理!E:E,MATCH(B280,商品管理!A:A,0)),"")</f>
-        <v/>
-      </c>
-      <c r="AE280" s="21" t="str" cm="1">
-        <f t="array" ref="AE280">IFERROR(INDEX(商品管理!F:F,MATCH(B280,商品管理!A:A,0)),"")</f>
-        <v/>
-      </c>
-      <c r="AF280" s="21" t="str" cm="1">
-        <f t="array" ref="AF280">IFERROR(INDEX(FBA仓库代码表!G:G,MATCH(E280,FBA仓库代码表!B:B,0)),"")</f>
-        <v/>
-      </c>
-      <c r="AG280" s="21" t="str" cm="1">
-        <f t="array" ref="AG280">IFERROR(INDEX(FBA仓库代码表!H:H,MATCH(E280,FBA仓库代码表!B:B,0)),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="281" spans="30:33">
-      <c r="AD281" s="21" t="str" cm="1">
-        <f t="array" ref="AD281">IFERROR(INDEX(商品管理!E:E,MATCH(B281,商品管理!A:A,0)),"")</f>
-        <v/>
-      </c>
-      <c r="AE281" s="21" t="str" cm="1">
-        <f t="array" ref="AE281">IFERROR(INDEX(商品管理!F:F,MATCH(B281,商品管理!A:A,0)),"")</f>
-        <v/>
-      </c>
-      <c r="AF281" s="21" t="str" cm="1">
-        <f t="array" ref="AF281">IFERROR(INDEX(FBA仓库代码表!G:G,MATCH(E281,FBA仓库代码表!B:B,0)),"")</f>
-        <v/>
-      </c>
-      <c r="AG281" s="21" t="str" cm="1">
-        <f t="array" ref="AG281">IFERROR(INDEX(FBA仓库代码表!H:H,MATCH(E281,FBA仓库代码表!B:B,0)),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="282" spans="30:33">
-      <c r="AD282" s="21" t="str" cm="1">
-        <f t="array" ref="AD282">IFERROR(INDEX(商品管理!E:E,MATCH(B282,商品管理!A:A,0)),"")</f>
-        <v/>
-      </c>
-      <c r="AE282" s="21" t="str" cm="1">
-        <f t="array" ref="AE282">IFERROR(INDEX(商品管理!F:F,MATCH(B282,商品管理!A:A,0)),"")</f>
-        <v/>
-      </c>
-      <c r="AF282" s="21" t="str" cm="1">
-        <f t="array" ref="AF282">IFERROR(INDEX(FBA仓库代码表!G:G,MATCH(E282,FBA仓库代码表!B:B,0)),"")</f>
-        <v/>
-      </c>
-      <c r="AG282" s="21" t="str" cm="1">
-        <f t="array" ref="AG282">IFERROR(INDEX(FBA仓库代码表!H:H,MATCH(E282,FBA仓库代码表!B:B,0)),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="283" spans="30:33">
-      <c r="AD283" s="21" t="str" cm="1">
-        <f t="array" ref="AD283">IFERROR(INDEX(商品管理!E:E,MATCH(B283,商品管理!A:A,0)),"")</f>
-        <v/>
-      </c>
-      <c r="AE283" s="21" t="str" cm="1">
-        <f t="array" ref="AE283">IFERROR(INDEX(商品管理!F:F,MATCH(B283,商品管理!A:A,0)),"")</f>
-        <v/>
-      </c>
-      <c r="AF283" s="21" t="str" cm="1">
-        <f t="array" ref="AF283">IFERROR(INDEX(FBA仓库代码表!G:G,MATCH(E283,FBA仓库代码表!B:B,0)),"")</f>
-        <v/>
-      </c>
-      <c r="AG283" s="21" t="str" cm="1">
-        <f t="array" ref="AG283">IFERROR(INDEX(FBA仓库代码表!H:H,MATCH(E283,FBA仓库代码表!B:B,0)),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="284" spans="30:33">
-      <c r="AD284" s="21" t="str" cm="1">
-        <f t="array" ref="AD284">IFERROR(INDEX(商品管理!E:E,MATCH(B284,商品管理!A:A,0)),"")</f>
-        <v/>
-      </c>
-      <c r="AE284" s="21" t="str" cm="1">
-        <f t="array" ref="AE284">IFERROR(INDEX(商品管理!F:F,MATCH(B284,商品管理!A:A,0)),"")</f>
-        <v/>
-      </c>
-      <c r="AF284" s="21" t="str" cm="1">
-        <f t="array" ref="AF284">IFERROR(INDEX(FBA仓库代码表!G:G,MATCH(E284,FBA仓库代码表!B:B,0)),"")</f>
-        <v/>
-      </c>
-      <c r="AG284" s="21" t="str" cm="1">
-        <f t="array" ref="AG284">IFERROR(INDEX(FBA仓库代码表!H:H,MATCH(E284,FBA仓库代码表!B:B,0)),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="285" spans="30:33">
-      <c r="AD285" s="21" t="str" cm="1">
-        <f t="array" ref="AD285">IFERROR(INDEX(商品管理!E:E,MATCH(B285,商品管理!A:A,0)),"")</f>
-        <v/>
-      </c>
-      <c r="AE285" s="21" t="str" cm="1">
-        <f t="array" ref="AE285">IFERROR(INDEX(商品管理!F:F,MATCH(B285,商品管理!A:A,0)),"")</f>
-        <v/>
-      </c>
-      <c r="AF285" s="21" t="str" cm="1">
-        <f t="array" ref="AF285">IFERROR(INDEX(FBA仓库代码表!G:G,MATCH(E285,FBA仓库代码表!B:B,0)),"")</f>
-        <v/>
-      </c>
-      <c r="AG285" s="21" t="str" cm="1">
-        <f t="array" ref="AG285">IFERROR(INDEX(FBA仓库代码表!H:H,MATCH(E285,FBA仓库代码表!B:B,0)),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="286" spans="30:33">
-      <c r="AD286" s="21" t="str" cm="1">
-        <f t="array" ref="AD286">IFERROR(INDEX(商品管理!E:E,MATCH(B286,商品管理!A:A,0)),"")</f>
-        <v/>
-      </c>
-      <c r="AE286" s="21" t="str" cm="1">
-        <f t="array" ref="AE286">IFERROR(INDEX(商品管理!F:F,MATCH(B286,商品管理!A:A,0)),"")</f>
-        <v/>
-      </c>
-      <c r="AF286" s="21" t="str" cm="1">
-        <f t="array" ref="AF286">IFERROR(INDEX(FBA仓库代码表!G:G,MATCH(E286,FBA仓库代码表!B:B,0)),"")</f>
-        <v/>
-      </c>
-      <c r="AG286" s="21" t="str" cm="1">
-        <f t="array" ref="AG286">IFERROR(INDEX(FBA仓库代码表!H:H,MATCH(E286,FBA仓库代码表!B:B,0)),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="287" spans="30:33">
-      <c r="AD287" s="21" t="str" cm="1">
-        <f t="array" ref="AD287">IFERROR(INDEX(商品管理!E:E,MATCH(B287,商品管理!A:A,0)),"")</f>
-        <v/>
-      </c>
-      <c r="AE287" s="21" t="str" cm="1">
-        <f t="array" ref="AE287">IFERROR(INDEX(商品管理!F:F,MATCH(B287,商品管理!A:A,0)),"")</f>
-        <v/>
-      </c>
-      <c r="AF287" s="21" t="str" cm="1">
-        <f t="array" ref="AF287">IFERROR(INDEX(FBA仓库代码表!G:G,MATCH(E287,FBA仓库代码表!B:B,0)),"")</f>
-        <v/>
-      </c>
-      <c r="AG287" s="21" t="str" cm="1">
-        <f t="array" ref="AG287">IFERROR(INDEX(FBA仓库代码表!H:H,MATCH(E287,FBA仓库代码表!B:B,0)),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="288" spans="30:33">
-      <c r="AD288" s="21" t="str" cm="1">
-        <f t="array" ref="AD288">IFERROR(INDEX(商品管理!E:E,MATCH(B288,商品管理!A:A,0)),"")</f>
-        <v/>
-      </c>
-      <c r="AE288" s="21" t="str" cm="1">
-        <f t="array" ref="AE288">IFERROR(INDEX(商品管理!F:F,MATCH(B288,商品管理!A:A,0)),"")</f>
-        <v/>
-      </c>
-      <c r="AF288" s="21" t="str" cm="1">
-        <f t="array" ref="AF288">IFERROR(INDEX(FBA仓库代码表!G:G,MATCH(E288,FBA仓库代码表!B:B,0)),"")</f>
-        <v/>
-      </c>
-      <c r="AG288" s="21" t="str" cm="1">
-        <f t="array" ref="AG288">IFERROR(INDEX(FBA仓库代码表!H:H,MATCH(E288,FBA仓库代码表!B:B,0)),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="289" spans="30:33">
-      <c r="AD289" s="21" t="str" cm="1">
-        <f t="array" ref="AD289">IFERROR(INDEX(商品管理!E:E,MATCH(B289,商品管理!A:A,0)),"")</f>
-        <v/>
-      </c>
-      <c r="AE289" s="21" t="str" cm="1">
-        <f t="array" ref="AE289">IFERROR(INDEX(商品管理!F:F,MATCH(B289,商品管理!A:A,0)),"")</f>
-        <v/>
-      </c>
-      <c r="AF289" s="21" t="str" cm="1">
-        <f t="array" ref="AF289">IFERROR(INDEX(FBA仓库代码表!G:G,MATCH(E289,FBA仓库代码表!B:B,0)),"")</f>
-        <v/>
-      </c>
-      <c r="AG289" s="21" t="str" cm="1">
-        <f t="array" ref="AG289">IFERROR(INDEX(FBA仓库代码表!H:H,MATCH(E289,FBA仓库代码表!B:B,0)),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="290" spans="30:33">
-      <c r="AD290" s="21" t="str" cm="1">
-        <f t="array" ref="AD290">IFERROR(INDEX(商品管理!E:E,MATCH(B290,商品管理!A:A,0)),"")</f>
-        <v/>
-      </c>
-      <c r="AE290" s="21" t="str" cm="1">
-        <f t="array" ref="AE290">IFERROR(INDEX(商品管理!F:F,MATCH(B290,商品管理!A:A,0)),"")</f>
-        <v/>
-      </c>
-      <c r="AF290" s="21" t="str" cm="1">
-        <f t="array" ref="AF290">IFERROR(INDEX(FBA仓库代码表!G:G,MATCH(E290,FBA仓库代码表!B:B,0)),"")</f>
-        <v/>
-      </c>
-      <c r="AG290" s="21" t="str" cm="1">
-        <f t="array" ref="AG290">IFERROR(INDEX(FBA仓库代码表!H:H,MATCH(E290,FBA仓库代码表!B:B,0)),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="291" spans="30:33">
-      <c r="AD291" s="21" t="str" cm="1">
-        <f t="array" ref="AD291">IFERROR(INDEX(商品管理!E:E,MATCH(B291,商品管理!A:A,0)),"")</f>
-        <v/>
-      </c>
-      <c r="AE291" s="21" t="str" cm="1">
-        <f t="array" ref="AE291">IFERROR(INDEX(商品管理!F:F,MATCH(B291,商品管理!A:A,0)),"")</f>
-        <v/>
-      </c>
-      <c r="AF291" s="21" t="str" cm="1">
-        <f t="array" ref="AF291">IFERROR(INDEX(FBA仓库代码表!G:G,MATCH(E291,FBA仓库代码表!B:B,0)),"")</f>
-        <v/>
-      </c>
-      <c r="AG291" s="21" t="str" cm="1">
-        <f t="array" ref="AG291">IFERROR(INDEX(FBA仓库代码表!H:H,MATCH(E291,FBA仓库代码表!B:B,0)),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="292" spans="30:33">
-      <c r="AD292" s="21" t="str" cm="1">
-        <f t="array" ref="AD292">IFERROR(INDEX(商品管理!E:E,MATCH(B292,商品管理!A:A,0)),"")</f>
-        <v/>
-      </c>
-      <c r="AE292" s="21" t="str" cm="1">
-        <f t="array" ref="AE292">IFERROR(INDEX(商品管理!F:F,MATCH(B292,商品管理!A:A,0)),"")</f>
-        <v/>
-      </c>
-      <c r="AF292" s="21" t="str" cm="1">
-        <f t="array" ref="AF292">IFERROR(INDEX(FBA仓库代码表!G:G,MATCH(E292,FBA仓库代码表!B:B,0)),"")</f>
-        <v/>
-      </c>
-      <c r="AG292" s="21" t="str" cm="1">
-        <f t="array" ref="AG292">IFERROR(INDEX(FBA仓库代码表!H:H,MATCH(E292,FBA仓库代码表!B:B,0)),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="293" spans="30:33">
-      <c r="AD293" s="21" t="str" cm="1">
-        <f t="array" ref="AD293">IFERROR(INDEX(商品管理!E:E,MATCH(B293,商品管理!A:A,0)),"")</f>
-        <v/>
-      </c>
-      <c r="AE293" s="21" t="str" cm="1">
-        <f t="array" ref="AE293">IFERROR(INDEX(商品管理!F:F,MATCH(B293,商品管理!A:A,0)),"")</f>
-        <v/>
-      </c>
-      <c r="AF293" s="21" t="str" cm="1">
-        <f t="array" ref="AF293">IFERROR(INDEX(FBA仓库代码表!G:G,MATCH(E293,FBA仓库代码表!B:B,0)),"")</f>
-        <v/>
-      </c>
-      <c r="AG293" s="21" t="str" cm="1">
-        <f t="array" ref="AG293">IFERROR(INDEX(FBA仓库代码表!H:H,MATCH(E293,FBA仓库代码表!B:B,0)),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="294" spans="30:33">
-      <c r="AD294" s="21" t="str" cm="1">
-        <f t="array" ref="AD294">IFERROR(INDEX(商品管理!E:E,MATCH(B294,商品管理!A:A,0)),"")</f>
-        <v/>
-      </c>
-      <c r="AE294" s="21" t="str" cm="1">
-        <f t="array" ref="AE294">IFERROR(INDEX(商品管理!F:F,MATCH(B294,商品管理!A:A,0)),"")</f>
-        <v/>
-      </c>
-      <c r="AF294" s="21" t="str" cm="1">
-        <f t="array" ref="AF294">IFERROR(INDEX(FBA仓库代码表!G:G,MATCH(E294,FBA仓库代码表!B:B,0)),"")</f>
-        <v/>
-      </c>
-      <c r="AG294" s="21" t="str" cm="1">
-        <f t="array" ref="AG294">IFERROR(INDEX(FBA仓库代码表!H:H,MATCH(E294,FBA仓库代码表!B:B,0)),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="295" spans="30:33">
-      <c r="AD295" s="21" t="str" cm="1">
-        <f t="array" ref="AD295">IFERROR(INDEX(商品管理!E:E,MATCH(B295,商品管理!A:A,0)),"")</f>
-        <v/>
-      </c>
-      <c r="AE295" s="21" t="str" cm="1">
-        <f t="array" ref="AE295">IFERROR(INDEX(商品管理!F:F,MATCH(B295,商品管理!A:A,0)),"")</f>
-        <v/>
-      </c>
-      <c r="AF295" s="21" t="str" cm="1">
-        <f t="array" ref="AF295">IFERROR(INDEX(FBA仓库代码表!G:G,MATCH(E295,FBA仓库代码表!B:B,0)),"")</f>
-        <v/>
-      </c>
-      <c r="AG295" s="21" t="str" cm="1">
-        <f t="array" ref="AG295">IFERROR(INDEX(FBA仓库代码表!H:H,MATCH(E295,FBA仓库代码表!B:B,0)),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="296" spans="30:33">
-      <c r="AD296" s="21" t="str" cm="1">
-        <f t="array" ref="AD296">IFERROR(INDEX(商品管理!E:E,MATCH(B296,商品管理!A:A,0)),"")</f>
-        <v/>
-      </c>
-      <c r="AE296" s="21" t="str" cm="1">
-        <f t="array" ref="AE296">IFERROR(INDEX(商品管理!F:F,MATCH(B296,商品管理!A:A,0)),"")</f>
-        <v/>
-      </c>
-      <c r="AF296" s="21" t="str" cm="1">
-        <f t="array" ref="AF296">IFERROR(INDEX(FBA仓库代码表!G:G,MATCH(E296,FBA仓库代码表!B:B,0)),"")</f>
-        <v/>
-      </c>
-      <c r="AG296" s="21" t="str" cm="1">
-        <f t="array" ref="AG296">IFERROR(INDEX(FBA仓库代码表!H:H,MATCH(E296,FBA仓库代码表!B:B,0)),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="297" spans="30:33">
-      <c r="AD297" s="21" t="str" cm="1">
-        <f t="array" ref="AD297">IFERROR(INDEX(商品管理!E:E,MATCH(B297,商品管理!A:A,0)),"")</f>
-        <v/>
-      </c>
-      <c r="AE297" s="21" t="str" cm="1">
-        <f t="array" ref="AE297">IFERROR(INDEX(商品管理!F:F,MATCH(B297,商品管理!A:A,0)),"")</f>
-        <v/>
-      </c>
-      <c r="AF297" s="21" t="str" cm="1">
-        <f t="array" ref="AF297">IFERROR(INDEX(FBA仓库代码表!G:G,MATCH(E297,FBA仓库代码表!B:B,0)),"")</f>
-        <v/>
-      </c>
-      <c r="AG297" s="21" t="str" cm="1">
-        <f t="array" ref="AG297">IFERROR(INDEX(FBA仓库代码表!H:H,MATCH(E297,FBA仓库代码表!B:B,0)),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="298" spans="30:33">
-      <c r="AD298" s="21" t="str" cm="1">
-        <f t="array" ref="AD298">IFERROR(INDEX(商品管理!E:E,MATCH(B298,商品管理!A:A,0)),"")</f>
-        <v/>
-      </c>
-      <c r="AE298" s="21" t="str" cm="1">
-        <f t="array" ref="AE298">IFERROR(INDEX(商品管理!F:F,MATCH(B298,商品管理!A:A,0)),"")</f>
-        <v/>
-      </c>
-      <c r="AF298" s="21" t="str" cm="1">
-        <f t="array" ref="AF298">IFERROR(INDEX(FBA仓库代码表!G:G,MATCH(E298,FBA仓库代码表!B:B,0)),"")</f>
-        <v/>
-      </c>
-      <c r="AG298" s="21" t="str" cm="1">
-        <f t="array" ref="AG298">IFERROR(INDEX(FBA仓库代码表!H:H,MATCH(E298,FBA仓库代码表!B:B,0)),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="299" spans="30:33">
-      <c r="AD299" s="21" t="str" cm="1">
-        <f t="array" ref="AD299">IFERROR(INDEX(商品管理!E:E,MATCH(B299,商品管理!A:A,0)),"")</f>
-        <v/>
-      </c>
-      <c r="AE299" s="21" t="str" cm="1">
-        <f t="array" ref="AE299">IFERROR(INDEX(商品管理!F:F,MATCH(B299,商品管理!A:A,0)),"")</f>
-        <v/>
-      </c>
-      <c r="AF299" s="21" t="str" cm="1">
-        <f t="array" ref="AF299">IFERROR(INDEX(FBA仓库代码表!G:G,MATCH(E299,FBA仓库代码表!B:B,0)),"")</f>
-        <v/>
-      </c>
-      <c r="AG299" s="21" t="str" cm="1">
-        <f t="array" ref="AG299">IFERROR(INDEX(FBA仓库代码表!H:H,MATCH(E299,FBA仓库代码表!B:B,0)),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="300" spans="30:33">
-      <c r="AD300" s="21" t="str" cm="1">
-        <f t="array" ref="AD300">IFERROR(INDEX(商品管理!E:E,MATCH(B300,商品管理!A:A,0)),"")</f>
-        <v/>
-      </c>
-      <c r="AE300" s="21" t="str" cm="1">
-        <f t="array" ref="AE300">IFERROR(INDEX(商品管理!F:F,MATCH(B300,商品管理!A:A,0)),"")</f>
-        <v/>
-      </c>
-      <c r="AF300" s="21" t="str" cm="1">
-        <f t="array" ref="AF300">IFERROR(INDEX(FBA仓库代码表!G:G,MATCH(E300,FBA仓库代码表!B:B,0)),"")</f>
-        <v/>
-      </c>
-      <c r="AG300" s="21" t="str" cm="1">
-        <f t="array" ref="AG300">IFERROR(INDEX(FBA仓库代码表!H:H,MATCH(E300,FBA仓库代码表!B:B,0)),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="301" spans="30:33">
-      <c r="AD301" s="21" t="str" cm="1">
-        <f t="array" ref="AD301">IFERROR(INDEX(商品管理!E:E,MATCH(B301,商品管理!A:A,0)),"")</f>
-        <v/>
-      </c>
-      <c r="AE301" s="21" t="str" cm="1">
-        <f t="array" ref="AE301">IFERROR(INDEX(商品管理!F:F,MATCH(B301,商品管理!A:A,0)),"")</f>
-        <v/>
-      </c>
-      <c r="AF301" s="21" t="str" cm="1">
-        <f t="array" ref="AF301">IFERROR(INDEX(FBA仓库代码表!G:G,MATCH(E301,FBA仓库代码表!B:B,0)),"")</f>
-        <v/>
-      </c>
-      <c r="AG301" s="21" t="str" cm="1">
-        <f t="array" ref="AG301">IFERROR(INDEX(FBA仓库代码表!H:H,MATCH(E301,FBA仓库代码表!B:B,0)),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="302" spans="30:33">
-      <c r="AD302" s="21" t="str" cm="1">
-        <f t="array" ref="AD302">IFERROR(INDEX(商品管理!E:E,MATCH(B302,商品管理!A:A,0)),"")</f>
-        <v/>
-      </c>
-      <c r="AF302" s="21" t="str" cm="1">
-        <f t="array" ref="AF302">IFERROR(INDEX(FBA仓库代码表!G:G,MATCH(E302,FBA仓库代码表!B:B,0)),"")</f>
-        <v/>
-      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -40993,7 +38103,7 @@
     <col min="16380" max="16384" width="9.64285714285714" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" spans="1:11">
+    <row r="1" s="1" customFormat="1" ht="16.8" spans="1:11">
       <c r="A1" s="4" t="s">
         <v>20</v>
       </c>
